--- a/figuras/tabela_1_pesada.xlsx
+++ b/figuras/tabela_1_pesada.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="630" uniqueCount="630">
   <si>
     <t xml:space="preserve">Characteristic
 </t>
@@ -24,7 +24,7 @@
     <t xml:space="preserve">peso_kg</t>
   </si>
   <si>
-    <t xml:space="preserve">     Unknown</t>
+    <t xml:space="preserve">    Unknown</t>
   </si>
   <si>
     <t xml:space="preserve">altura_cm</t>
@@ -39,58 +39,58 @@
     <t xml:space="preserve">cor</t>
   </si>
   <si>
-    <t xml:space="preserve">     amarela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">     branca</t>
-  </si>
-  <si>
-    <t xml:space="preserve">     indigena</t>
-  </si>
-  <si>
-    <t xml:space="preserve">     nao_respondeu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">     nao_sabe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">     parda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">     preta</t>
+    <t xml:space="preserve">    amarela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    branca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    indigena</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    nao_respondeu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    nao_sabe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    parda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    preta</t>
   </si>
   <si>
     <t xml:space="preserve">escolaridade_cat_num</t>
   </si>
   <si>
-    <t xml:space="preserve">     0-4 anos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">     12 ou mais anos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">     5-8 anos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">     9-11 anos</t>
+    <t xml:space="preserve">    0-4 anos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    12 ou mais anos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    5-8 anos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    9-11 anos</t>
   </si>
   <si>
     <t xml:space="preserve">macro_reg</t>
   </si>
   <si>
-    <t xml:space="preserve">     Centro-Oeste</t>
-  </si>
-  <si>
-    <t xml:space="preserve">     Nordeste</t>
-  </si>
-  <si>
-    <t xml:space="preserve">     Norte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">     Sudeste</t>
-  </si>
-  <si>
-    <t xml:space="preserve">     Sul</t>
+    <t xml:space="preserve">    Centro-Oeste</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Nordeste</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Norte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Sudeste</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Sul</t>
   </si>
   <si>
     <t xml:space="preserve">trabalha</t>
@@ -132,10 +132,10 @@
     <t xml:space="preserve">ativamente_fisico_desloc_novo</t>
   </si>
   <si>
-    <t xml:space="preserve">     não</t>
-  </si>
-  <si>
-    <t xml:space="preserve">     sim</t>
+    <t xml:space="preserve">    não</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    sim</t>
   </si>
   <si>
     <t xml:space="preserve">ativamente_fisico_desloc_num</t>
@@ -144,38 +144,39 @@
     <t xml:space="preserve">cat_ativ</t>
   </si>
   <si>
-    <t xml:space="preserve">     Não realiza</t>
-  </si>
-  <si>
-    <t xml:space="preserve">     &gt;0 e ≤30 minutos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">     &gt;30 e ≤60 minutos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">     &gt;60 minutos</t>
+    <t xml:space="preserve">    Não realiza</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    &gt;0 e ≤30 minutos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    &gt;30 e ≤60 minutos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    &gt;60 minutos</t>
   </si>
   <si>
     <t xml:space="preserve">ativamente_fisico_desloc</t>
   </si>
   <si>
-    <t xml:space="preserve">Mean (SD); % %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2009, N = 32,485,702
+    <t xml:space="preserve">Mean (SD); %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2009
+N = 32,485,702
 </t>
   </si>
   <si>
     <t xml:space="preserve">2,009.0 (0.0)</t>
   </si>
   <si>
-    <t xml:space="preserve">70 (15)</t>
+    <t xml:space="preserve">69.8 (14.8)</t>
   </si>
   <si>
     <t xml:space="preserve">1,046,097</t>
   </si>
   <si>
-    <t xml:space="preserve">166 (10)</t>
+    <t xml:space="preserve">166.4 (9.9)</t>
   </si>
   <si>
     <t xml:space="preserve">2,189,059</t>
@@ -184,702 +185,1469 @@
     <t xml:space="preserve"/>
   </si>
   <si>
-    <t xml:space="preserve">17 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.5 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;0.1 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.1 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36 %</t>
+    <t xml:space="preserve">17.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.8%</t>
   </si>
   <si>
     <t xml:space="preserve">42,481</t>
   </si>
   <si>
-    <t xml:space="preserve">26 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.2 %</t>
+    <t xml:space="preserve">11.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.2%</t>
   </si>
   <si>
     <t xml:space="preserve">11,626,296</t>
   </si>
   <si>
-    <t xml:space="preserve">29 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.8 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2,659 (3,239)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12 (20)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2010, N = 33,423,349
+    <t xml:space="preserve">57.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,659.2 (3,239.1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3 (20.0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2010
+N = 33,423,349
 </t>
   </si>
   <si>
     <t xml:space="preserve">2,010.0 (0.0)</t>
   </si>
   <si>
+    <t xml:space="preserve">70.3 (15.0)</t>
+  </si>
+  <si>
     <t xml:space="preserve">1,315,737</t>
   </si>
   <si>
+    <t xml:space="preserve">166.4 (10.2)</t>
+  </si>
+  <si>
     <t xml:space="preserve">2,423,712</t>
   </si>
   <si>
-    <t xml:space="preserve">10 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.4 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0 %</t>
+    <t xml:space="preserve">17.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8%</t>
   </si>
   <si>
     <t xml:space="preserve">43,850</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65 %</t>
+    <t xml:space="preserve">25.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.7%</t>
   </si>
   <si>
     <t xml:space="preserve">11,601,640</t>
   </si>
   <si>
-    <t xml:space="preserve">56 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NA %</t>
+    <t xml:space="preserve">56.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NA%</t>
   </si>
   <si>
     <t xml:space="preserve">33,423,349</t>
   </si>
   <si>
-    <t xml:space="preserve">2,821 (3,811)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2011, N = 33,702,305
+    <t xml:space="preserve">2,820.7 (3,811.3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4 (20.2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2011
+N = 33,702,305
 </t>
   </si>
   <si>
     <t xml:space="preserve">2,011.0 (0.0)</t>
   </si>
   <si>
-    <t xml:space="preserve">71 (15)</t>
+    <t xml:space="preserve">70.9 (15.1)</t>
   </si>
   <si>
     <t xml:space="preserve">1,384,989</t>
   </si>
   <si>
+    <t xml:space="preserve">166.5 (10.0)</t>
+  </si>
+  <si>
     <t xml:space="preserve">2,185,710</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37 %</t>
+    <t xml:space="preserve">16.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.7%</t>
   </si>
   <si>
     <t xml:space="preserve">62,293</t>
   </si>
   <si>
-    <t xml:space="preserve">66 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69 %</t>
+    <t xml:space="preserve">11.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.2%</t>
   </si>
   <si>
     <t xml:space="preserve">11,548,630</t>
   </si>
   <si>
-    <t xml:space="preserve">87 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75 %</t>
+    <t xml:space="preserve">54.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.6%</t>
   </si>
   <si>
     <t xml:space="preserve">33,702,305</t>
   </si>
   <si>
-    <t xml:space="preserve">2,477 (2,753)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11 (19)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2012, N = 33,972,289
+    <t xml:space="preserve">2,477.5 (2,753.1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3 (19.1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2012
+N = 33,972,289
 </t>
   </si>
   <si>
     <t xml:space="preserve">2,012.0 (0.0)</t>
   </si>
   <si>
-    <t xml:space="preserve">72 (15)</t>
+    <t xml:space="preserve">71.6 (15.5)</t>
   </si>
   <si>
     <t xml:space="preserve">1,320,177</t>
   </si>
   <si>
-    <t xml:space="preserve">167 (10)</t>
+    <t xml:space="preserve">166.8 (10.0)</t>
   </si>
   <si>
     <t xml:space="preserve">2,265,399</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.3 %</t>
+    <t xml:space="preserve">25.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3%</t>
   </si>
   <si>
     <t xml:space="preserve">11,577,563</t>
   </si>
   <si>
-    <t xml:space="preserve">73 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92 %</t>
+    <t xml:space="preserve">56.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.5%</t>
   </si>
   <si>
     <t xml:space="preserve">33,972,289</t>
   </si>
   <si>
-    <t xml:space="preserve">3,044 (3,424)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11 (18)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2013, N = 34,245,016
+    <t xml:space="preserve">3,043.9 (3,424.4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7 (18.3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2013
+N = 34,245,016
 </t>
   </si>
   <si>
     <t xml:space="preserve">2,013.0 (0.0)</t>
   </si>
   <si>
-    <t xml:space="preserve">72 (16)</t>
+    <t xml:space="preserve">71.7 (15.6)</t>
   </si>
   <si>
     <t xml:space="preserve">1,552,163</t>
   </si>
   <si>
+    <t xml:space="preserve">166.8 (10.3)</t>
+  </si>
+  <si>
     <t xml:space="preserve">2,349,078</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4 %</t>
+    <t xml:space="preserve">25.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.3%</t>
   </si>
   <si>
     <t xml:space="preserve">131,567</t>
   </si>
   <si>
-    <t xml:space="preserve">27 %</t>
+    <t xml:space="preserve">64.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.8%</t>
   </si>
   <si>
     <t xml:space="preserve">12,155,475</t>
   </si>
   <si>
-    <t xml:space="preserve">59 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.7 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2,672 (2,916)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10 (17)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2014, N = 34,520,527
+    <t xml:space="preserve">54.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,672.4 (2,916.1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6 (17.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2014
+N = 34,520,527
 </t>
   </si>
   <si>
     <t xml:space="preserve">2,014.0 (0.0)</t>
   </si>
   <si>
+    <t xml:space="preserve">71.8 (15.3)</t>
+  </si>
+  <si>
     <t xml:space="preserve">1,525,757</t>
   </si>
   <si>
+    <t xml:space="preserve">166.5 (10.3)</t>
+  </si>
+  <si>
     <t xml:space="preserve">2,198,244</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51 %</t>
+    <t xml:space="preserve">15.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.7%</t>
   </si>
   <si>
     <t xml:space="preserve">12,411,660</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6 %</t>
+    <t xml:space="preserve">55.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.9%</t>
   </si>
   <si>
     <t xml:space="preserve">34,520,527</t>
   </si>
   <si>
-    <t xml:space="preserve">78 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3,561 (4,210)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2015, N = 34,798,855
+    <t xml:space="preserve">78.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,561.3 (4,210.2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7 (17.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2015
+N = 34,798,855
 </t>
   </si>
   <si>
     <t xml:space="preserve">2,015.0 (0.0)</t>
   </si>
   <si>
+    <t xml:space="preserve">72.5 (15.7)</t>
+  </si>
+  <si>
     <t xml:space="preserve">1,998,835</t>
   </si>
   <si>
+    <t xml:space="preserve">166.6 (10.3)</t>
+  </si>
+  <si>
     <t xml:space="preserve">2,492,244</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0 %</t>
+    <t xml:space="preserve">10.8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0%</t>
   </si>
   <si>
     <t xml:space="preserve">3,785,014</t>
   </si>
   <si>
-    <t xml:space="preserve">14 %</t>
+    <t xml:space="preserve">13.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.9%</t>
   </si>
   <si>
     <t xml:space="preserve">13,027,848</t>
   </si>
   <si>
-    <t xml:space="preserve">60 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.6 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">77 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3,202 (3,915)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9 (17)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2016, N = 35,080,036
+    <t xml:space="preserve">55.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">77.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,202.0 (3,915.0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2 (16.8)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2016
+N = 35,080,036
 </t>
   </si>
   <si>
     <t xml:space="preserve">2,016.0 (0.0)</t>
   </si>
   <si>
-    <t xml:space="preserve">73 (16)</t>
+    <t xml:space="preserve">72.5 (15.6)</t>
   </si>
   <si>
     <t xml:space="preserve">1,348,519</t>
   </si>
   <si>
+    <t xml:space="preserve">166.7 (10.3)</t>
+  </si>
+  <si>
     <t xml:space="preserve">2,069,380</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6 %</t>
+    <t xml:space="preserve">14.8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.5%</t>
   </si>
   <si>
     <t xml:space="preserve">12,421,432</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3,012 (3,407)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10 (18)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2017, N = 35,364,106
+    <t xml:space="preserve">55.8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,012.4 (3,407.0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3 (18.2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2017
+N = 35,364,106
 </t>
   </si>
   <si>
     <t xml:space="preserve">2,017.0 (0.0)</t>
   </si>
   <si>
+    <t xml:space="preserve">72.7 (15.7)</t>
+  </si>
+  <si>
     <t xml:space="preserve">1,646,869</t>
   </si>
   <si>
+    <t xml:space="preserve">166.9 (10.3)</t>
+  </si>
+  <si>
     <t xml:space="preserve">2,095,539</t>
   </si>
   <si>
-    <t xml:space="preserve">0.9 %</t>
+    <t xml:space="preserve">14.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.9%</t>
   </si>
   <si>
     <t xml:space="preserve">2,302,206</t>
   </si>
   <si>
+    <t xml:space="preserve">13.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.3%</t>
+  </si>
+  <si>
     <t xml:space="preserve">12,682,743</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6 %</t>
+    <t xml:space="preserve">55.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6%</t>
   </si>
   <si>
     <t xml:space="preserve">35,364,106</t>
   </si>
   <si>
-    <t xml:space="preserve">3,218 (3,621)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2018, N = 35,651,103
+    <t xml:space="preserve">3,218.1 (3,621.4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8 (17.8)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2018
+N = 35,651,103
 </t>
   </si>
   <si>
     <t xml:space="preserve">2,018.0 (0.0)</t>
   </si>
   <si>
+    <t xml:space="preserve">73.0 (16.1)</t>
+  </si>
+  <si>
     <t xml:space="preserve">1,478,674</t>
   </si>
   <si>
+    <t xml:space="preserve">166.7 (10.2)</t>
+  </si>
+  <si>
     <t xml:space="preserve">1,983,474</t>
   </si>
   <si>
-    <t xml:space="preserve">42 %</t>
+    <t xml:space="preserve">14.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.6%</t>
   </si>
   <si>
     <t xml:space="preserve">2,466,328</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0 %</t>
+    <t xml:space="preserve">13.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.2%</t>
   </si>
   <si>
     <t xml:space="preserve">12,849,020</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7 %</t>
+    <t xml:space="preserve">54.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7%</t>
   </si>
   <si>
     <t xml:space="preserve">35,651,103</t>
   </si>
   <si>
-    <t xml:space="preserve">3,175 (3,869)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2019, N = 35,941,061
+    <t xml:space="preserve">3,175.2 (3,869.2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1 (18.3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2019
+N = 35,941,061
 </t>
   </si>
   <si>
     <t xml:space="preserve">2,019.0 (0.0)</t>
   </si>
   <si>
+    <t xml:space="preserve">73.1 (16.0)</t>
+  </si>
+  <si>
     <t xml:space="preserve">1,816,422</t>
   </si>
   <si>
     <t xml:space="preserve">2,099,838</t>
   </si>
   <si>
+    <t xml:space="preserve">13.8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.5%</t>
+  </si>
+  <si>
     <t xml:space="preserve">2,127,371</t>
   </si>
   <si>
+    <t xml:space="preserve">32.8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.8%</t>
+  </si>
+  <si>
     <t xml:space="preserve">13,080,161</t>
   </si>
   <si>
+    <t xml:space="preserve">54.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.4%</t>
+  </si>
+  <si>
     <t xml:space="preserve">35,941,061</t>
   </si>
   <si>
-    <t xml:space="preserve">3,393 (4,123)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10 (19)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2020, N = 36,234,023
+    <t xml:space="preserve">3,393.1 (4,123.0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2 (18.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020
+N = 36,234,023
 </t>
   </si>
   <si>
     <t xml:space="preserve">2,020.0 (0.0)</t>
   </si>
   <si>
-    <t xml:space="preserve">74 (16)</t>
+    <t xml:space="preserve">73.9 (16.1)</t>
   </si>
   <si>
     <t xml:space="preserve">1,845,446</t>
@@ -888,66 +1656,200 @@
     <t xml:space="preserve">1,943,330</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0 %</t>
+    <t xml:space="preserve">13.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.9%</t>
   </si>
   <si>
     <t xml:space="preserve">1,506,611</t>
   </si>
   <si>
+    <t xml:space="preserve">33.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.1%</t>
+  </si>
+  <si>
     <t xml:space="preserve">13,322,747</t>
   </si>
   <si>
+    <t xml:space="preserve">54.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.8%</t>
+  </si>
+  <si>
     <t xml:space="preserve">36,234,023</t>
   </si>
   <si>
-    <t xml:space="preserve">7,579 (9,902)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021, N = 36,478,037
+    <t xml:space="preserve">7,579.2 (9,901.7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8 (18.0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021
+N = 36,478,037
 </t>
   </si>
   <si>
     <t xml:space="preserve">2,021.0 (0.0)</t>
   </si>
   <si>
+    <t xml:space="preserve">73.8 (16.2)</t>
+  </si>
+  <si>
     <t xml:space="preserve">1,890,022</t>
   </si>
   <si>
+    <t xml:space="preserve">166.6 (10.0)</t>
+  </si>
+  <si>
     <t xml:space="preserve">1,651,026</t>
   </si>
   <si>
+    <t xml:space="preserve">13.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5%</t>
+  </si>
+  <si>
     <t xml:space="preserve">1,084,366</t>
   </si>
   <si>
+    <t xml:space="preserve">11.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.2%</t>
+  </si>
+  <si>
     <t xml:space="preserve">14,649,812</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2 %</t>
+    <t xml:space="preserve">51.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.6%</t>
   </si>
   <si>
     <t xml:space="preserve">36,478,037</t>
   </si>
   <si>
-    <t xml:space="preserve">8,843 (12,027)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8 (16)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2023, N = 37,040,957
+    <t xml:space="preserve">8,843.5 (12,026.7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9 (16.4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023
+N = 37,040,957
 </t>
   </si>
   <si>
     <t xml:space="preserve">2,023.0 (0.0)</t>
   </si>
   <si>
-    <t xml:space="preserve">75 (17)</t>
+    <t xml:space="preserve">75.1 (17.1)</t>
   </si>
   <si>
     <t xml:space="preserve">1,305,990</t>
@@ -956,25 +1858,79 @@
     <t xml:space="preserve">1,497,371</t>
   </si>
   <si>
+    <t xml:space="preserve">18.3%</t>
+  </si>
+  <si>
     <t xml:space="preserve">791,062</t>
   </si>
   <si>
-    <t xml:space="preserve">58 %</t>
+    <t xml:space="preserve">32.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.6%</t>
   </si>
   <si>
     <t xml:space="preserve">14,071,883</t>
   </si>
   <si>
+    <t xml:space="preserve">47.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.7%</t>
+  </si>
+  <si>
     <t xml:space="preserve">1,148</t>
   </si>
   <si>
+    <t xml:space="preserve">27.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.7%</t>
+  </si>
+  <si>
     <t xml:space="preserve">37,040,957</t>
   </si>
   <si>
-    <t xml:space="preserve">8,753 (12,072)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4 %</t>
+    <t xml:space="preserve">8,752.6 (12,071.6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8 (17.4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4%</t>
   </si>
 </sst>
 </file>
@@ -1436,43 +2392,43 @@
         <v>49</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>130</v>
+        <v>161</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>157</v>
+        <v>212</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>180</v>
+        <v>254</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>201</v>
+        <v>299</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>217</v>
+        <v>342</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>236</v>
+        <v>387</v>
       </c>
       <c r="J1" s="6" t="s">
-        <v>249</v>
+        <v>426</v>
       </c>
       <c r="K1" s="6" t="s">
-        <v>262</v>
+        <v>464</v>
       </c>
       <c r="L1" s="6" t="s">
-        <v>273</v>
+        <v>502</v>
       </c>
       <c r="M1" s="6" t="s">
-        <v>282</v>
+        <v>534</v>
       </c>
       <c r="N1" s="6" t="s">
-        <v>293</v>
+        <v>568</v>
       </c>
       <c r="O1" s="6" t="s">
-        <v>304</v>
+        <v>600</v>
       </c>
     </row>
     <row r="2" ht="NA" customHeight="1">
@@ -1483,43 +2439,43 @@
         <v>50</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>131</v>
+        <v>162</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>158</v>
+        <v>213</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>181</v>
+        <v>255</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>202</v>
+        <v>300</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>218</v>
+        <v>343</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>237</v>
+        <v>388</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>250</v>
+        <v>427</v>
       </c>
       <c r="K2" s="7" t="s">
-        <v>263</v>
+        <v>465</v>
       </c>
       <c r="L2" s="7" t="s">
-        <v>274</v>
+        <v>503</v>
       </c>
       <c r="M2" s="7" t="s">
-        <v>283</v>
+        <v>535</v>
       </c>
       <c r="N2" s="7" t="s">
-        <v>294</v>
+        <v>569</v>
       </c>
       <c r="O2" s="7" t="s">
-        <v>305</v>
+        <v>601</v>
       </c>
     </row>
     <row r="3" ht="NA" customHeight="1">
@@ -1530,43 +2486,43 @@
         <v>51</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>51</v>
+        <v>112</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>132</v>
+        <v>163</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>159</v>
+        <v>214</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>182</v>
+        <v>256</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>159</v>
+        <v>301</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>182</v>
+        <v>344</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>238</v>
+        <v>389</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>238</v>
+        <v>428</v>
       </c>
       <c r="K3" s="8" t="s">
-        <v>238</v>
+        <v>466</v>
       </c>
       <c r="L3" s="8" t="s">
-        <v>238</v>
+        <v>504</v>
       </c>
       <c r="M3" s="8" t="s">
-        <v>284</v>
+        <v>536</v>
       </c>
       <c r="N3" s="8" t="s">
-        <v>284</v>
+        <v>570</v>
       </c>
       <c r="O3" s="8" t="s">
-        <v>306</v>
+        <v>602</v>
       </c>
     </row>
     <row r="4" ht="NA" customHeight="1">
@@ -1577,43 +2533,43 @@
         <v>52</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>133</v>
+        <v>164</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>160</v>
+        <v>215</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>183</v>
+        <v>257</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>203</v>
+        <v>302</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>219</v>
+        <v>345</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>239</v>
+        <v>390</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>251</v>
+        <v>429</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>264</v>
+        <v>467</v>
       </c>
       <c r="L4" s="8" t="s">
-        <v>275</v>
+        <v>505</v>
       </c>
       <c r="M4" s="8" t="s">
-        <v>285</v>
+        <v>537</v>
       </c>
       <c r="N4" s="8" t="s">
-        <v>295</v>
+        <v>571</v>
       </c>
       <c r="O4" s="8" t="s">
-        <v>307</v>
+        <v>603</v>
       </c>
     </row>
     <row r="5" ht="NA" customHeight="1">
@@ -1624,43 +2580,43 @@
         <v>53</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>53</v>
+        <v>114</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>53</v>
+        <v>165</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>161</v>
+        <v>216</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>161</v>
+        <v>258</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>53</v>
+        <v>303</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>161</v>
+        <v>346</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>161</v>
+        <v>391</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>161</v>
+        <v>430</v>
       </c>
       <c r="K5" s="8" t="s">
-        <v>161</v>
+        <v>468</v>
       </c>
       <c r="L5" s="8" t="s">
-        <v>161</v>
+        <v>391</v>
       </c>
       <c r="M5" s="8" t="s">
-        <v>161</v>
+        <v>468</v>
       </c>
       <c r="N5" s="8" t="s">
-        <v>161</v>
+        <v>572</v>
       </c>
       <c r="O5" s="8" t="s">
-        <v>161</v>
+        <v>468</v>
       </c>
     </row>
     <row r="6" ht="NA" customHeight="1">
@@ -1671,43 +2627,43 @@
         <v>54</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>134</v>
+        <v>166</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>162</v>
+        <v>217</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>184</v>
+        <v>259</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>204</v>
+        <v>304</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>220</v>
+        <v>347</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>240</v>
+        <v>392</v>
       </c>
       <c r="J6" s="8" t="s">
-        <v>252</v>
+        <v>431</v>
       </c>
       <c r="K6" s="8" t="s">
-        <v>265</v>
+        <v>469</v>
       </c>
       <c r="L6" s="8" t="s">
-        <v>276</v>
+        <v>506</v>
       </c>
       <c r="M6" s="8" t="s">
-        <v>286</v>
+        <v>538</v>
       </c>
       <c r="N6" s="8" t="s">
-        <v>296</v>
+        <v>573</v>
       </c>
       <c r="O6" s="8" t="s">
-        <v>308</v>
+        <v>604</v>
       </c>
     </row>
     <row r="7" ht="NA" customHeight="1">
@@ -1765,43 +2721,43 @@
         <v>56</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>56</v>
+        <v>116</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>56</v>
+        <v>167</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>59</v>
+        <v>118</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>59</v>
+        <v>208</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>59</v>
+        <v>305</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>76</v>
+        <v>130</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>76</v>
+        <v>393</v>
       </c>
       <c r="J8" s="8" t="s">
-        <v>226</v>
+        <v>432</v>
       </c>
       <c r="K8" s="8" t="s">
-        <v>226</v>
+        <v>470</v>
       </c>
       <c r="L8" s="8" t="s">
-        <v>226</v>
+        <v>507</v>
       </c>
       <c r="M8" s="8" t="s">
-        <v>199</v>
+        <v>539</v>
       </c>
       <c r="N8" s="8" t="s">
-        <v>199</v>
+        <v>574</v>
       </c>
       <c r="O8" s="8" t="s">
-        <v>199</v>
+        <v>295</v>
       </c>
     </row>
     <row r="9" ht="NA" customHeight="1">
@@ -1818,37 +2774,37 @@
         <v>57</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>57</v>
+        <v>218</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>57</v>
+        <v>260</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>57</v>
+        <v>260</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>57</v>
+        <v>218</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>57</v>
+        <v>218</v>
       </c>
       <c r="J9" s="8" t="s">
-        <v>57</v>
+        <v>218</v>
       </c>
       <c r="K9" s="8" t="s">
-        <v>57</v>
+        <v>184</v>
       </c>
       <c r="L9" s="8" t="s">
-        <v>57</v>
+        <v>129</v>
       </c>
       <c r="M9" s="8" t="s">
-        <v>57</v>
+        <v>129</v>
       </c>
       <c r="N9" s="8" t="s">
-        <v>57</v>
+        <v>129</v>
       </c>
       <c r="O9" s="8" t="s">
-        <v>57</v>
+        <v>376</v>
       </c>
     </row>
     <row r="10" ht="NA" customHeight="1">
@@ -1859,43 +2815,43 @@
         <v>58</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>58</v>
+        <v>117</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>58</v>
+        <v>168</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>58</v>
+        <v>196</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>58</v>
+        <v>261</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>58</v>
+        <v>306</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>126</v>
+        <v>280</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>126</v>
+        <v>368</v>
       </c>
       <c r="J10" s="8" t="s">
-        <v>126</v>
+        <v>433</v>
       </c>
       <c r="K10" s="8" t="s">
-        <v>126</v>
+        <v>471</v>
       </c>
       <c r="L10" s="8" t="s">
-        <v>126</v>
+        <v>157</v>
       </c>
       <c r="M10" s="8" t="s">
-        <v>126</v>
+        <v>540</v>
       </c>
       <c r="N10" s="8" t="s">
-        <v>126</v>
+        <v>575</v>
       </c>
       <c r="O10" s="8" t="s">
-        <v>70</v>
+        <v>605</v>
       </c>
     </row>
     <row r="11" ht="NA" customHeight="1">
@@ -1906,43 +2862,43 @@
         <v>59</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>59</v>
+        <v>118</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>56</v>
+        <v>169</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>56</v>
+        <v>125</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>56</v>
+        <v>262</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>56</v>
+        <v>116</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>56</v>
+        <v>178</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>56</v>
+        <v>394</v>
       </c>
       <c r="J11" s="8" t="s">
-        <v>70</v>
+        <v>434</v>
       </c>
       <c r="K11" s="8" t="s">
-        <v>70</v>
+        <v>472</v>
       </c>
       <c r="L11" s="8" t="s">
-        <v>70</v>
+        <v>106</v>
       </c>
       <c r="M11" s="8" t="s">
         <v>70</v>
       </c>
       <c r="N11" s="8" t="s">
-        <v>70</v>
+        <v>576</v>
       </c>
       <c r="O11" s="8" t="s">
-        <v>70</v>
+        <v>605</v>
       </c>
     </row>
     <row r="12" ht="NA" customHeight="1">
@@ -1953,43 +2909,43 @@
         <v>60</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>60</v>
+        <v>119</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>60</v>
+        <v>170</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>60</v>
+        <v>219</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>88</v>
+        <v>263</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>88</v>
+        <v>145</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>88</v>
+        <v>395</v>
       </c>
       <c r="J12" s="8" t="s">
-        <v>199</v>
+        <v>435</v>
       </c>
       <c r="K12" s="8" t="s">
-        <v>199</v>
+        <v>384</v>
       </c>
       <c r="L12" s="8" t="s">
-        <v>199</v>
+        <v>508</v>
       </c>
       <c r="M12" s="8" t="s">
-        <v>199</v>
+        <v>539</v>
       </c>
       <c r="N12" s="8" t="s">
-        <v>199</v>
+        <v>577</v>
       </c>
       <c r="O12" s="8" t="s">
-        <v>226</v>
+        <v>507</v>
       </c>
     </row>
     <row r="13" ht="NA" customHeight="1">
@@ -2000,43 +2956,43 @@
         <v>61</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>107</v>
+        <v>171</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>107</v>
+        <v>220</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>107</v>
+        <v>177</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>60</v>
+        <v>307</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>60</v>
+        <v>348</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>60</v>
+        <v>119</v>
       </c>
       <c r="J13" s="8" t="s">
-        <v>60</v>
+        <v>170</v>
       </c>
       <c r="K13" s="8" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="L13" s="8" t="s">
-        <v>60</v>
+        <v>219</v>
       </c>
       <c r="M13" s="8" t="s">
-        <v>88</v>
+        <v>317</v>
       </c>
       <c r="N13" s="8" t="s">
-        <v>88</v>
+        <v>263</v>
       </c>
       <c r="O13" s="8" t="s">
-        <v>88</v>
+        <v>145</v>
       </c>
     </row>
     <row r="14" ht="NA" customHeight="1">
@@ -2109,28 +3065,28 @@
         <v>62</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>62</v>
+        <v>349</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>62</v>
+        <v>349</v>
       </c>
       <c r="J15" s="8" t="s">
-        <v>62</v>
+        <v>349</v>
       </c>
       <c r="K15" s="8" t="s">
-        <v>62</v>
+        <v>349</v>
       </c>
       <c r="L15" s="8" t="s">
-        <v>62</v>
+        <v>349</v>
       </c>
       <c r="M15" s="8" t="s">
-        <v>62</v>
+        <v>349</v>
       </c>
       <c r="N15" s="8" t="s">
-        <v>62</v>
+        <v>349</v>
       </c>
       <c r="O15" s="8" t="s">
-        <v>62</v>
+        <v>349</v>
       </c>
     </row>
     <row r="16" ht="NA" customHeight="1">
@@ -2156,28 +3112,28 @@
         <v>63</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>63</v>
+        <v>350</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>63</v>
+        <v>350</v>
       </c>
       <c r="J16" s="8" t="s">
-        <v>63</v>
+        <v>350</v>
       </c>
       <c r="K16" s="8" t="s">
-        <v>63</v>
+        <v>350</v>
       </c>
       <c r="L16" s="8" t="s">
-        <v>63</v>
+        <v>350</v>
       </c>
       <c r="M16" s="8" t="s">
-        <v>63</v>
+        <v>350</v>
       </c>
       <c r="N16" s="8" t="s">
-        <v>63</v>
+        <v>350</v>
       </c>
       <c r="O16" s="8" t="s">
-        <v>63</v>
+        <v>350</v>
       </c>
     </row>
     <row r="17" ht="NA" customHeight="1">
@@ -2235,43 +3191,43 @@
         <v>64</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>135</v>
+        <v>172</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>163</v>
+        <v>221</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>119</v>
+        <v>146</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>205</v>
+        <v>308</v>
       </c>
       <c r="H18" s="8" t="s">
-        <v>221</v>
+        <v>351</v>
       </c>
       <c r="I18" s="8" t="s">
-        <v>213</v>
+        <v>332</v>
       </c>
       <c r="J18" s="8" t="s">
-        <v>223</v>
+        <v>354</v>
       </c>
       <c r="K18" s="8" t="s">
-        <v>196</v>
+        <v>291</v>
       </c>
       <c r="L18" s="8" t="s">
-        <v>253</v>
+        <v>437</v>
       </c>
       <c r="M18" s="8" t="s">
-        <v>287</v>
+        <v>541</v>
       </c>
       <c r="N18" s="8" t="s">
-        <v>138</v>
+        <v>175</v>
       </c>
       <c r="O18" s="8" t="s">
-        <v>223</v>
+        <v>354</v>
       </c>
     </row>
     <row r="19" ht="NA" customHeight="1">
@@ -2282,43 +3238,43 @@
         <v>65</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>77</v>
+        <v>122</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>136</v>
+        <v>173</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>139</v>
+        <v>222</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>139</v>
+        <v>264</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>77</v>
+        <v>309</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>62</v>
+        <v>352</v>
       </c>
       <c r="I19" s="8" t="s">
-        <v>136</v>
+        <v>396</v>
       </c>
       <c r="J19" s="8" t="s">
-        <v>143</v>
+        <v>436</v>
       </c>
       <c r="K19" s="8" t="s">
-        <v>136</v>
+        <v>473</v>
       </c>
       <c r="L19" s="8" t="s">
-        <v>136</v>
+        <v>396</v>
       </c>
       <c r="M19" s="8" t="s">
-        <v>80</v>
+        <v>134</v>
       </c>
       <c r="N19" s="8" t="s">
-        <v>139</v>
+        <v>176</v>
       </c>
       <c r="O19" s="8" t="s">
-        <v>65</v>
+        <v>480</v>
       </c>
     </row>
     <row r="20" ht="NA" customHeight="1">
@@ -2329,43 +3285,43 @@
         <v>66</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>137</v>
+        <v>174</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>164</v>
+        <v>223</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>185</v>
+        <v>265</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>206</v>
+        <v>310</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>222</v>
+        <v>353</v>
       </c>
       <c r="I20" s="8" t="s">
-        <v>222</v>
+        <v>353</v>
       </c>
       <c r="J20" s="8" t="s">
-        <v>206</v>
+        <v>310</v>
       </c>
       <c r="K20" s="8" t="s">
-        <v>196</v>
+        <v>291</v>
       </c>
       <c r="L20" s="8" t="s">
-        <v>196</v>
+        <v>291</v>
       </c>
       <c r="M20" s="8" t="s">
-        <v>137</v>
+        <v>174</v>
       </c>
       <c r="N20" s="8" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="O20" s="8" t="s">
-        <v>253</v>
+        <v>437</v>
       </c>
     </row>
     <row r="21" ht="NA" customHeight="1">
@@ -2373,31 +3329,31 @@
         <v>11</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C21" s="8" t="s">
         <v>66</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H21" s="8" t="s">
-        <v>191</v>
+        <v>284</v>
       </c>
       <c r="I21" s="8" t="s">
-        <v>229</v>
+        <v>373</v>
       </c>
       <c r="J21" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K21" s="8" t="s">
         <v>67</v>
@@ -2409,10 +3365,10 @@
         <v>67</v>
       </c>
       <c r="N21" s="8" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="O21" s="8" t="s">
-        <v>168</v>
+        <v>237</v>
       </c>
     </row>
     <row r="22" ht="NA" customHeight="1">
@@ -2426,28 +3382,28 @@
         <v>67</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>138</v>
+        <v>175</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>186</v>
+        <v>266</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>207</v>
+        <v>311</v>
       </c>
       <c r="H22" s="8" t="s">
-        <v>223</v>
+        <v>354</v>
       </c>
       <c r="I22" s="8" t="s">
-        <v>241</v>
+        <v>397</v>
       </c>
       <c r="J22" s="8" t="s">
-        <v>253</v>
+        <v>437</v>
       </c>
       <c r="K22" s="8" t="s">
-        <v>229</v>
+        <v>373</v>
       </c>
       <c r="L22" s="8" t="s">
         <v>64</v>
@@ -2456,10 +3412,10 @@
         <v>64</v>
       </c>
       <c r="N22" s="8" t="s">
-        <v>229</v>
+        <v>373</v>
       </c>
       <c r="O22" s="8" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
     </row>
     <row r="23" ht="NA" customHeight="1">
@@ -2470,43 +3426,43 @@
         <v>68</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>139</v>
+        <v>176</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>140</v>
+        <v>224</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>73</v>
+        <v>267</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>73</v>
+        <v>312</v>
       </c>
       <c r="H23" s="8" t="s">
-        <v>208</v>
+        <v>355</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>140</v>
+        <v>224</v>
       </c>
       <c r="J23" s="8" t="s">
-        <v>77</v>
+        <v>309</v>
       </c>
       <c r="K23" s="8" t="s">
-        <v>266</v>
+        <v>474</v>
       </c>
       <c r="L23" s="8" t="s">
-        <v>266</v>
+        <v>509</v>
       </c>
       <c r="M23" s="8" t="s">
-        <v>266</v>
+        <v>542</v>
       </c>
       <c r="N23" s="8" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="O23" s="8" t="s">
-        <v>136</v>
+        <v>447</v>
       </c>
     </row>
     <row r="24" ht="NA" customHeight="1">
@@ -2517,43 +3473,43 @@
         <v>69</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>60</v>
+        <v>177</v>
       </c>
       <c r="E24" s="8" t="s">
         <v>60</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>60</v>
+        <v>177</v>
       </c>
       <c r="H24" s="8" t="s">
-        <v>224</v>
+        <v>356</v>
       </c>
       <c r="I24" s="8" t="s">
-        <v>242</v>
+        <v>398</v>
       </c>
       <c r="J24" s="8" t="s">
-        <v>88</v>
+        <v>263</v>
       </c>
       <c r="K24" s="8" t="s">
-        <v>60</v>
+        <v>119</v>
       </c>
       <c r="L24" s="8" t="s">
-        <v>60</v>
+        <v>183</v>
       </c>
       <c r="M24" s="8" t="s">
-        <v>60</v>
+        <v>170</v>
       </c>
       <c r="N24" s="8" t="s">
-        <v>226</v>
+        <v>399</v>
       </c>
       <c r="O24" s="8" t="s">
-        <v>199</v>
+        <v>539</v>
       </c>
     </row>
     <row r="25" ht="NA" customHeight="1">
@@ -2579,28 +3535,28 @@
         <v>0</v>
       </c>
       <c r="H25" s="8" t="s">
-        <v>225</v>
+        <v>357</v>
       </c>
       <c r="I25" s="8" t="n">
         <v>0</v>
       </c>
       <c r="J25" s="8" t="s">
-        <v>254</v>
+        <v>438</v>
       </c>
       <c r="K25" s="8" t="s">
-        <v>267</v>
+        <v>475</v>
       </c>
       <c r="L25" s="8" t="s">
-        <v>277</v>
+        <v>510</v>
       </c>
       <c r="M25" s="8" t="s">
-        <v>288</v>
+        <v>543</v>
       </c>
       <c r="N25" s="8" t="s">
-        <v>297</v>
+        <v>578</v>
       </c>
       <c r="O25" s="8" t="s">
-        <v>309</v>
+        <v>606</v>
       </c>
     </row>
     <row r="26" ht="NA" customHeight="1">
@@ -2658,43 +3614,43 @@
         <v>70</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>56</v>
+        <v>125</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>56</v>
+        <v>178</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>59</v>
+        <v>225</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>76</v>
+        <v>130</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>76</v>
+        <v>313</v>
       </c>
       <c r="H27" s="8" t="s">
-        <v>226</v>
+        <v>358</v>
       </c>
       <c r="I27" s="8" t="s">
-        <v>226</v>
+        <v>399</v>
       </c>
       <c r="J27" s="8" t="s">
-        <v>199</v>
+        <v>439</v>
       </c>
       <c r="K27" s="8" t="s">
-        <v>199</v>
+        <v>476</v>
       </c>
       <c r="L27" s="8" t="s">
-        <v>199</v>
+        <v>384</v>
       </c>
       <c r="M27" s="8" t="s">
-        <v>88</v>
+        <v>145</v>
       </c>
       <c r="N27" s="8" t="s">
-        <v>88</v>
+        <v>579</v>
       </c>
       <c r="O27" s="8" t="s">
-        <v>60</v>
+        <v>170</v>
       </c>
     </row>
     <row r="28" ht="NA" customHeight="1">
@@ -2705,43 +3661,43 @@
         <v>71</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>72</v>
+        <v>126</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>57</v>
+        <v>179</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>57</v>
+        <v>226</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>75</v>
+        <v>268</v>
       </c>
       <c r="G28" s="8" t="s">
-        <v>75</v>
+        <v>314</v>
       </c>
       <c r="H28" s="8" t="s">
-        <v>188</v>
+        <v>359</v>
       </c>
       <c r="I28" s="8" t="s">
-        <v>179</v>
+        <v>400</v>
       </c>
       <c r="J28" s="8" t="s">
-        <v>179</v>
+        <v>253</v>
       </c>
       <c r="K28" s="8" t="s">
-        <v>179</v>
+        <v>477</v>
       </c>
       <c r="L28" s="8" t="s">
-        <v>156</v>
+        <v>511</v>
       </c>
       <c r="M28" s="8" t="s">
-        <v>129</v>
+        <v>544</v>
       </c>
       <c r="N28" s="8" t="s">
-        <v>156</v>
+        <v>580</v>
       </c>
       <c r="O28" s="8" t="s">
-        <v>156</v>
+        <v>607</v>
       </c>
     </row>
     <row r="29" ht="NA" customHeight="1">
@@ -2752,43 +3708,43 @@
         <v>72</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>71</v>
+        <v>180</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>165</v>
+        <v>227</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>165</v>
+        <v>269</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>165</v>
+        <v>315</v>
       </c>
       <c r="H29" s="8" t="s">
-        <v>165</v>
+        <v>227</v>
       </c>
       <c r="I29" s="8" t="s">
-        <v>126</v>
+        <v>401</v>
       </c>
       <c r="J29" s="8" t="s">
-        <v>70</v>
+        <v>434</v>
       </c>
       <c r="K29" s="8" t="s">
-        <v>56</v>
+        <v>178</v>
       </c>
       <c r="L29" s="8" t="s">
-        <v>59</v>
+        <v>512</v>
       </c>
       <c r="M29" s="8" t="s">
-        <v>59</v>
+        <v>305</v>
       </c>
       <c r="N29" s="8" t="s">
-        <v>76</v>
+        <v>393</v>
       </c>
       <c r="O29" s="8" t="s">
-        <v>76</v>
+        <v>608</v>
       </c>
     </row>
     <row r="30" ht="NA" customHeight="1">
@@ -2802,40 +3758,40 @@
         <v>73</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>140</v>
+        <v>181</v>
       </c>
       <c r="E30" s="8" t="s">
-        <v>65</v>
+        <v>228</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>140</v>
+        <v>270</v>
       </c>
       <c r="G30" s="8" t="s">
-        <v>208</v>
+        <v>316</v>
       </c>
       <c r="H30" s="8" t="s">
-        <v>208</v>
+        <v>316</v>
       </c>
       <c r="I30" s="8" t="s">
-        <v>73</v>
+        <v>402</v>
       </c>
       <c r="J30" s="8" t="s">
-        <v>140</v>
+        <v>270</v>
       </c>
       <c r="K30" s="8" t="s">
-        <v>208</v>
+        <v>478</v>
       </c>
       <c r="L30" s="8" t="s">
-        <v>208</v>
+        <v>355</v>
       </c>
       <c r="M30" s="8" t="s">
-        <v>65</v>
+        <v>545</v>
       </c>
       <c r="N30" s="8" t="s">
-        <v>77</v>
+        <v>122</v>
       </c>
       <c r="O30" s="8" t="s">
-        <v>139</v>
+        <v>609</v>
       </c>
     </row>
     <row r="31" ht="NA" customHeight="1">
@@ -2846,16 +3802,16 @@
         <v>74</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>111</v>
+        <v>128</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>141</v>
+        <v>182</v>
       </c>
       <c r="E31" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>187</v>
+        <v>271</v>
       </c>
       <c r="G31" s="8" t="n">
         <v>0</v>
@@ -2937,46 +3893,46 @@
         <v>21</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>60</v>
+        <v>183</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>60</v>
+        <v>219</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>60</v>
+        <v>219</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>60</v>
+        <v>317</v>
       </c>
       <c r="H33" s="8" t="s">
-        <v>88</v>
+        <v>317</v>
       </c>
       <c r="I33" s="8" t="s">
-        <v>88</v>
+        <v>263</v>
       </c>
       <c r="J33" s="8" t="s">
-        <v>88</v>
+        <v>263</v>
       </c>
       <c r="K33" s="8" t="s">
-        <v>88</v>
+        <v>479</v>
       </c>
       <c r="L33" s="8" t="s">
-        <v>88</v>
+        <v>479</v>
       </c>
       <c r="M33" s="8" t="s">
-        <v>88</v>
+        <v>145</v>
       </c>
       <c r="N33" s="8" t="s">
-        <v>88</v>
+        <v>145</v>
       </c>
       <c r="O33" s="8" t="s">
-        <v>88</v>
+        <v>579</v>
       </c>
     </row>
     <row r="34" ht="NA" customHeight="1">
@@ -2984,46 +3940,46 @@
         <v>22</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>57</v>
+        <v>129</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>57</v>
+        <v>184</v>
       </c>
       <c r="E34" s="8" t="s">
-        <v>57</v>
+        <v>184</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>57</v>
+        <v>184</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>57</v>
+        <v>184</v>
       </c>
       <c r="H34" s="8" t="s">
-        <v>57</v>
+        <v>184</v>
       </c>
       <c r="I34" s="8" t="s">
-        <v>57</v>
+        <v>218</v>
       </c>
       <c r="J34" s="8" t="s">
-        <v>57</v>
+        <v>218</v>
       </c>
       <c r="K34" s="8" t="s">
-        <v>57</v>
+        <v>218</v>
       </c>
       <c r="L34" s="8" t="s">
-        <v>57</v>
+        <v>218</v>
       </c>
       <c r="M34" s="8" t="s">
-        <v>57</v>
+        <v>260</v>
       </c>
       <c r="N34" s="8" t="s">
-        <v>57</v>
+        <v>260</v>
       </c>
       <c r="O34" s="8" t="s">
-        <v>57</v>
+        <v>260</v>
       </c>
     </row>
     <row r="35" ht="NA" customHeight="1">
@@ -3031,46 +3987,46 @@
         <v>23</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>76</v>
+        <v>130</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>76</v>
+        <v>185</v>
       </c>
       <c r="E35" s="8" t="s">
-        <v>76</v>
+        <v>185</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>76</v>
+        <v>185</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>76</v>
+        <v>318</v>
       </c>
       <c r="H35" s="8" t="s">
-        <v>76</v>
+        <v>318</v>
       </c>
       <c r="I35" s="8" t="s">
-        <v>76</v>
+        <v>403</v>
       </c>
       <c r="J35" s="8" t="s">
-        <v>59</v>
+        <v>403</v>
       </c>
       <c r="K35" s="8" t="s">
-        <v>59</v>
+        <v>305</v>
       </c>
       <c r="L35" s="8" t="s">
-        <v>59</v>
+        <v>305</v>
       </c>
       <c r="M35" s="8" t="s">
-        <v>59</v>
+        <v>546</v>
       </c>
       <c r="N35" s="8" t="s">
-        <v>59</v>
+        <v>546</v>
       </c>
       <c r="O35" s="8" t="s">
-        <v>59</v>
+        <v>610</v>
       </c>
     </row>
     <row r="36" ht="NA" customHeight="1">
@@ -3078,46 +4034,46 @@
         <v>24</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>77</v>
+        <v>131</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>77</v>
+        <v>186</v>
       </c>
       <c r="E36" s="8" t="s">
-        <v>77</v>
+        <v>229</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>77</v>
+        <v>122</v>
       </c>
       <c r="G36" s="8" t="s">
-        <v>77</v>
+        <v>319</v>
       </c>
       <c r="H36" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I36" s="8" t="s">
-        <v>77</v>
+        <v>309</v>
       </c>
       <c r="J36" s="8" t="s">
-        <v>77</v>
+        <v>440</v>
       </c>
       <c r="K36" s="8" t="s">
-        <v>65</v>
+        <v>480</v>
       </c>
       <c r="L36" s="8" t="s">
-        <v>65</v>
+        <v>513</v>
       </c>
       <c r="M36" s="8" t="s">
-        <v>65</v>
+        <v>547</v>
       </c>
       <c r="N36" s="8" t="s">
         <v>65</v>
       </c>
       <c r="O36" s="8" t="s">
-        <v>65</v>
+        <v>611</v>
       </c>
     </row>
     <row r="37" ht="NA" customHeight="1">
@@ -3125,46 +4081,46 @@
         <v>25</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>112</v>
+        <v>132</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>112</v>
+        <v>132</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>166</v>
+        <v>230</v>
       </c>
       <c r="F37" s="8" t="s">
-        <v>166</v>
+        <v>230</v>
       </c>
       <c r="G37" s="8" t="s">
-        <v>166</v>
+        <v>230</v>
       </c>
       <c r="H37" s="8" t="s">
-        <v>166</v>
+        <v>230</v>
       </c>
       <c r="I37" s="8" t="s">
-        <v>166</v>
+        <v>230</v>
       </c>
       <c r="J37" s="8" t="s">
-        <v>166</v>
+        <v>230</v>
       </c>
       <c r="K37" s="8" t="s">
-        <v>268</v>
+        <v>481</v>
       </c>
       <c r="L37" s="8" t="s">
-        <v>268</v>
+        <v>481</v>
       </c>
       <c r="M37" s="8" t="s">
-        <v>268</v>
+        <v>481</v>
       </c>
       <c r="N37" s="8" t="s">
-        <v>268</v>
+        <v>481</v>
       </c>
       <c r="O37" s="8" t="s">
-        <v>268</v>
+        <v>481</v>
       </c>
     </row>
     <row r="38" ht="NA" customHeight="1">
@@ -3219,46 +4175,46 @@
         <v>1</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>113</v>
+        <v>133</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>142</v>
+        <v>187</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>142</v>
+        <v>231</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>113</v>
+        <v>272</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>79</v>
+        <v>320</v>
       </c>
       <c r="H39" s="8" t="s">
-        <v>154</v>
+        <v>360</v>
       </c>
       <c r="I39" s="8" t="s">
-        <v>113</v>
+        <v>404</v>
       </c>
       <c r="J39" s="8" t="s">
-        <v>79</v>
+        <v>441</v>
       </c>
       <c r="K39" s="8" t="s">
-        <v>79</v>
+        <v>320</v>
       </c>
       <c r="L39" s="8" t="s">
-        <v>79</v>
+        <v>514</v>
       </c>
       <c r="M39" s="8" t="s">
-        <v>154</v>
+        <v>548</v>
       </c>
       <c r="N39" s="8" t="s">
-        <v>228</v>
+        <v>581</v>
       </c>
       <c r="O39" s="8" t="s">
-        <v>127</v>
+        <v>612</v>
       </c>
     </row>
     <row r="40" ht="NA" customHeight="1">
@@ -3269,43 +4225,43 @@
         <v>73</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>129</v>
+        <v>188</v>
       </c>
       <c r="E40" s="8" t="s">
-        <v>129</v>
+        <v>232</v>
       </c>
       <c r="F40" s="8" t="s">
-        <v>102</v>
+        <v>273</v>
       </c>
       <c r="G40" s="8" t="s">
-        <v>73</v>
+        <v>312</v>
       </c>
       <c r="H40" s="8" t="s">
-        <v>140</v>
+        <v>361</v>
       </c>
       <c r="I40" s="8" t="s">
-        <v>102</v>
+        <v>405</v>
       </c>
       <c r="J40" s="8" t="s">
-        <v>73</v>
+        <v>402</v>
       </c>
       <c r="K40" s="8" t="s">
-        <v>73</v>
+        <v>312</v>
       </c>
       <c r="L40" s="8" t="s">
-        <v>73</v>
+        <v>515</v>
       </c>
       <c r="M40" s="8" t="s">
-        <v>140</v>
+        <v>549</v>
       </c>
       <c r="N40" s="8" t="s">
-        <v>77</v>
+        <v>186</v>
       </c>
       <c r="O40" s="8" t="s">
-        <v>208</v>
+        <v>478</v>
       </c>
     </row>
     <row r="41" ht="NA" customHeight="1">
@@ -3360,46 +4316,46 @@
         <v>1</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>80</v>
+        <v>134</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>143</v>
+        <v>189</v>
       </c>
       <c r="E42" s="8" t="s">
-        <v>167</v>
+        <v>233</v>
       </c>
       <c r="F42" s="8" t="s">
-        <v>167</v>
+        <v>274</v>
       </c>
       <c r="G42" s="8" t="s">
-        <v>209</v>
+        <v>321</v>
       </c>
       <c r="H42" s="8" t="s">
-        <v>210</v>
+        <v>362</v>
       </c>
       <c r="I42" s="8" t="s">
-        <v>63</v>
+        <v>406</v>
       </c>
       <c r="J42" s="8" t="s">
-        <v>68</v>
+        <v>442</v>
       </c>
       <c r="K42" s="8" t="s">
-        <v>144</v>
+        <v>482</v>
       </c>
       <c r="L42" s="8" t="s">
-        <v>115</v>
+        <v>516</v>
       </c>
       <c r="M42" s="8" t="s">
-        <v>115</v>
+        <v>550</v>
       </c>
       <c r="N42" s="8" t="s">
-        <v>115</v>
+        <v>582</v>
       </c>
       <c r="O42" s="8" t="s">
-        <v>310</v>
+        <v>613</v>
       </c>
     </row>
     <row r="43" ht="NA" customHeight="1">
@@ -3407,46 +4363,46 @@
         <v>2</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>81</v>
+        <v>135</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>144</v>
+        <v>190</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>68</v>
+        <v>234</v>
       </c>
       <c r="F43" s="8" t="s">
         <v>68</v>
       </c>
       <c r="G43" s="8" t="s">
-        <v>210</v>
+        <v>322</v>
       </c>
       <c r="H43" s="8" t="s">
-        <v>209</v>
+        <v>363</v>
       </c>
       <c r="I43" s="8" t="s">
-        <v>62</v>
+        <v>407</v>
       </c>
       <c r="J43" s="8" t="s">
-        <v>167</v>
+        <v>443</v>
       </c>
       <c r="K43" s="8" t="s">
-        <v>143</v>
+        <v>326</v>
       </c>
       <c r="L43" s="8" t="s">
-        <v>136</v>
+        <v>517</v>
       </c>
       <c r="M43" s="8" t="s">
-        <v>136</v>
+        <v>367</v>
       </c>
       <c r="N43" s="8" t="s">
-        <v>136</v>
+        <v>473</v>
       </c>
       <c r="O43" s="8" t="s">
-        <v>266</v>
+        <v>614</v>
       </c>
     </row>
     <row r="44" ht="NA" customHeight="1">
@@ -3501,46 +4457,46 @@
         <v>1</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>145</v>
+        <v>191</v>
       </c>
       <c r="E45" s="8" t="s">
-        <v>145</v>
+        <v>235</v>
       </c>
       <c r="F45" s="8" t="s">
-        <v>188</v>
+        <v>275</v>
       </c>
       <c r="G45" s="8" t="s">
-        <v>75</v>
+        <v>314</v>
       </c>
       <c r="H45" s="8" t="s">
         <v>57</v>
       </c>
       <c r="I45" s="8" t="s">
-        <v>86</v>
+        <v>408</v>
       </c>
       <c r="J45" s="8" t="s">
-        <v>86</v>
+        <v>413</v>
       </c>
       <c r="K45" s="8" t="s">
-        <v>82</v>
+        <v>483</v>
       </c>
       <c r="L45" s="8" t="s">
-        <v>86</v>
+        <v>386</v>
       </c>
       <c r="M45" s="8" t="s">
-        <v>145</v>
+        <v>551</v>
       </c>
       <c r="N45" s="8" t="s">
-        <v>86</v>
+        <v>583</v>
       </c>
       <c r="O45" s="8" t="s">
-        <v>82</v>
+        <v>136</v>
       </c>
     </row>
     <row r="46" ht="NA" customHeight="1">
@@ -3548,46 +4504,46 @@
         <v>2</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>83</v>
+        <v>137</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>146</v>
+        <v>192</v>
       </c>
       <c r="E46" s="8" t="s">
-        <v>146</v>
+        <v>236</v>
       </c>
       <c r="F46" s="8" t="s">
-        <v>170</v>
+        <v>276</v>
       </c>
       <c r="G46" s="8" t="s">
-        <v>91</v>
+        <v>323</v>
       </c>
       <c r="H46" s="8" t="s">
-        <v>91</v>
+        <v>364</v>
       </c>
       <c r="I46" s="8" t="s">
-        <v>87</v>
+        <v>409</v>
       </c>
       <c r="J46" s="8" t="s">
-        <v>87</v>
+        <v>444</v>
       </c>
       <c r="K46" s="8" t="s">
-        <v>83</v>
+        <v>484</v>
       </c>
       <c r="L46" s="8" t="s">
-        <v>87</v>
+        <v>518</v>
       </c>
       <c r="M46" s="8" t="s">
-        <v>146</v>
+        <v>552</v>
       </c>
       <c r="N46" s="8" t="s">
-        <v>87</v>
+        <v>584</v>
       </c>
       <c r="O46" s="8" t="s">
-        <v>83</v>
+        <v>615</v>
       </c>
     </row>
     <row r="47" ht="NA" customHeight="1">
@@ -3595,34 +4551,34 @@
         <v>777</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D47" s="8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E47" s="8" t="s">
-        <v>168</v>
+        <v>237</v>
       </c>
       <c r="F47" s="8" t="s">
         <v>64</v>
       </c>
       <c r="G47" s="8" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="H47" s="8" t="s">
-        <v>191</v>
+        <v>284</v>
       </c>
       <c r="I47" s="8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J47" s="8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K47" s="8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="L47" s="8" t="s">
         <v>66</v>
@@ -3634,7 +4590,7 @@
         <v>67</v>
       </c>
       <c r="O47" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="48" ht="NA" customHeight="1">
@@ -3642,46 +4598,46 @@
         <v>3</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C48" s="8" t="s">
-        <v>114</v>
+        <v>138</v>
       </c>
       <c r="D48" s="8" t="s">
-        <v>147</v>
+        <v>193</v>
       </c>
       <c r="E48" s="8" t="s">
-        <v>169</v>
+        <v>238</v>
       </c>
       <c r="F48" s="8" t="s">
-        <v>189</v>
+        <v>277</v>
       </c>
       <c r="G48" s="8" t="s">
-        <v>211</v>
+        <v>324</v>
       </c>
       <c r="H48" s="8" t="s">
-        <v>227</v>
+        <v>365</v>
       </c>
       <c r="I48" s="8" t="s">
-        <v>243</v>
+        <v>410</v>
       </c>
       <c r="J48" s="8" t="s">
-        <v>255</v>
+        <v>445</v>
       </c>
       <c r="K48" s="8" t="s">
-        <v>269</v>
+        <v>485</v>
       </c>
       <c r="L48" s="8" t="s">
-        <v>278</v>
+        <v>519</v>
       </c>
       <c r="M48" s="8" t="s">
-        <v>289</v>
+        <v>553</v>
       </c>
       <c r="N48" s="8" t="s">
-        <v>298</v>
+        <v>585</v>
       </c>
       <c r="O48" s="8" t="s">
-        <v>311</v>
+        <v>616</v>
       </c>
     </row>
     <row r="49" ht="NA" customHeight="1">
@@ -3736,46 +4692,46 @@
         <v>1</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="C50" s="8" t="s">
-        <v>115</v>
+        <v>139</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>144</v>
+        <v>194</v>
       </c>
       <c r="E50" s="8" t="s">
-        <v>115</v>
+        <v>239</v>
       </c>
       <c r="F50" s="8" t="s">
-        <v>144</v>
+        <v>278</v>
       </c>
       <c r="G50" s="8" t="s">
-        <v>144</v>
+        <v>325</v>
       </c>
       <c r="H50" s="8" t="s">
-        <v>144</v>
+        <v>366</v>
       </c>
       <c r="I50" s="8" t="s">
-        <v>115</v>
+        <v>411</v>
       </c>
       <c r="J50" s="8" t="s">
-        <v>115</v>
+        <v>446</v>
       </c>
       <c r="K50" s="8" t="s">
-        <v>63</v>
+        <v>486</v>
       </c>
       <c r="L50" s="8" t="s">
-        <v>63</v>
+        <v>520</v>
       </c>
       <c r="M50" s="8" t="s">
-        <v>63</v>
+        <v>554</v>
       </c>
       <c r="N50" s="8" t="s">
-        <v>210</v>
+        <v>586</v>
       </c>
       <c r="O50" s="8" t="s">
-        <v>167</v>
+        <v>617</v>
       </c>
     </row>
     <row r="51" ht="NA" customHeight="1">
@@ -3783,46 +4739,46 @@
         <v>2</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="C51" s="8" t="s">
-        <v>80</v>
+        <v>134</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>143</v>
+        <v>195</v>
       </c>
       <c r="E51" s="8" t="s">
-        <v>80</v>
+        <v>173</v>
       </c>
       <c r="F51" s="8" t="s">
-        <v>143</v>
+        <v>279</v>
       </c>
       <c r="G51" s="8" t="s">
-        <v>136</v>
+        <v>326</v>
       </c>
       <c r="H51" s="8" t="s">
-        <v>136</v>
+        <v>367</v>
       </c>
       <c r="I51" s="8" t="s">
-        <v>136</v>
+        <v>367</v>
       </c>
       <c r="J51" s="8" t="s">
-        <v>136</v>
+        <v>447</v>
       </c>
       <c r="K51" s="8" t="s">
-        <v>62</v>
+        <v>487</v>
       </c>
       <c r="L51" s="8" t="s">
-        <v>143</v>
+        <v>189</v>
       </c>
       <c r="M51" s="8" t="s">
-        <v>62</v>
+        <v>555</v>
       </c>
       <c r="N51" s="8" t="s">
-        <v>209</v>
+        <v>587</v>
       </c>
       <c r="O51" s="8" t="s">
-        <v>68</v>
+        <v>618</v>
       </c>
     </row>
     <row r="52" ht="NA" customHeight="1">
@@ -3830,31 +4786,31 @@
         <v>777</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C52" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D52" s="8" t="s">
         <v>67</v>
       </c>
       <c r="E52" s="8" t="s">
-        <v>168</v>
+        <v>237</v>
       </c>
       <c r="F52" s="8" t="s">
         <v>64</v>
       </c>
       <c r="G52" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H52" s="8" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="I52" s="8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J52" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K52" s="8" t="s">
         <v>67</v>
@@ -3866,7 +4822,7 @@
         <v>67</v>
       </c>
       <c r="N52" s="8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O52" s="8" t="s">
         <v>66</v>
@@ -3877,46 +4833,46 @@
         <v>3</v>
       </c>
       <c r="B53" s="8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C53" s="8" t="s">
-        <v>114</v>
+        <v>138</v>
       </c>
       <c r="D53" s="8" t="s">
-        <v>147</v>
+        <v>193</v>
       </c>
       <c r="E53" s="8" t="s">
-        <v>169</v>
+        <v>238</v>
       </c>
       <c r="F53" s="8" t="s">
-        <v>189</v>
+        <v>277</v>
       </c>
       <c r="G53" s="8" t="s">
-        <v>211</v>
+        <v>324</v>
       </c>
       <c r="H53" s="8" t="s">
-        <v>227</v>
+        <v>365</v>
       </c>
       <c r="I53" s="8" t="s">
-        <v>243</v>
+        <v>410</v>
       </c>
       <c r="J53" s="8" t="s">
-        <v>255</v>
+        <v>445</v>
       </c>
       <c r="K53" s="8" t="s">
-        <v>269</v>
+        <v>485</v>
       </c>
       <c r="L53" s="8" t="s">
-        <v>278</v>
+        <v>519</v>
       </c>
       <c r="M53" s="8" t="s">
-        <v>289</v>
+        <v>553</v>
       </c>
       <c r="N53" s="8" t="s">
-        <v>298</v>
+        <v>585</v>
       </c>
       <c r="O53" s="8" t="s">
-        <v>311</v>
+        <v>616</v>
       </c>
     </row>
     <row r="54" ht="NA" customHeight="1">
@@ -3971,46 +4927,46 @@
         <v>1</v>
       </c>
       <c r="B55" s="8" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="C55" s="8" t="s">
-        <v>58</v>
+        <v>140</v>
       </c>
       <c r="D55" s="8" t="s">
-        <v>58</v>
+        <v>196</v>
       </c>
       <c r="E55" s="8" t="s">
-        <v>126</v>
+        <v>240</v>
       </c>
       <c r="F55" s="8" t="s">
-        <v>126</v>
+        <v>280</v>
       </c>
       <c r="G55" s="8" t="s">
-        <v>126</v>
+        <v>157</v>
       </c>
       <c r="H55" s="8" t="s">
-        <v>126</v>
+        <v>368</v>
       </c>
       <c r="I55" s="8" t="s">
+        <v>262</v>
+      </c>
+      <c r="J55" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="J55" s="8" t="s">
-        <v>70</v>
-      </c>
       <c r="K55" s="8" t="s">
-        <v>59</v>
+        <v>225</v>
       </c>
       <c r="L55" s="8" t="s">
-        <v>56</v>
+        <v>521</v>
       </c>
       <c r="M55" s="8" t="s">
-        <v>56</v>
+        <v>556</v>
       </c>
       <c r="N55" s="8" t="s">
-        <v>126</v>
+        <v>240</v>
       </c>
       <c r="O55" s="8" t="s">
-        <v>70</v>
+        <v>106</v>
       </c>
     </row>
     <row r="56" ht="NA" customHeight="1">
@@ -4018,46 +4974,46 @@
         <v>2</v>
       </c>
       <c r="B56" s="8" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="C56" s="8" t="s">
-        <v>116</v>
+        <v>141</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>72</v>
+        <v>197</v>
       </c>
       <c r="E56" s="8" t="s">
-        <v>72</v>
+        <v>197</v>
       </c>
       <c r="F56" s="8" t="s">
-        <v>165</v>
+        <v>269</v>
       </c>
       <c r="G56" s="8" t="s">
-        <v>116</v>
+        <v>327</v>
       </c>
       <c r="H56" s="8" t="s">
-        <v>165</v>
+        <v>369</v>
       </c>
       <c r="I56" s="8" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="J56" s="8" t="s">
-        <v>165</v>
+        <v>448</v>
       </c>
       <c r="K56" s="8" t="s">
-        <v>71</v>
+        <v>488</v>
       </c>
       <c r="L56" s="8" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="M56" s="8" t="s">
-        <v>116</v>
+        <v>557</v>
       </c>
       <c r="N56" s="8" t="s">
-        <v>56</v>
+        <v>394</v>
       </c>
       <c r="O56" s="8" t="s">
-        <v>56</v>
+        <v>394</v>
       </c>
     </row>
     <row r="57" ht="NA" customHeight="1">
@@ -4065,46 +5021,46 @@
         <v>3</v>
       </c>
       <c r="B57" s="8" t="s">
-        <v>63</v>
+        <v>91</v>
       </c>
       <c r="C57" s="8" t="s">
-        <v>115</v>
+        <v>142</v>
       </c>
       <c r="D57" s="8" t="s">
-        <v>115</v>
+        <v>198</v>
       </c>
       <c r="E57" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F57" s="8" t="s">
-        <v>190</v>
+        <v>281</v>
       </c>
       <c r="G57" s="8" t="s">
-        <v>190</v>
+        <v>328</v>
       </c>
       <c r="H57" s="8" t="s">
-        <v>228</v>
+        <v>370</v>
       </c>
       <c r="I57" s="8" t="s">
-        <v>190</v>
+        <v>412</v>
       </c>
       <c r="J57" s="8" t="s">
-        <v>99</v>
+        <v>449</v>
       </c>
       <c r="K57" s="8" t="s">
-        <v>127</v>
+        <v>489</v>
       </c>
       <c r="L57" s="8" t="s">
-        <v>99</v>
+        <v>522</v>
       </c>
       <c r="M57" s="8" t="s">
-        <v>228</v>
+        <v>558</v>
       </c>
       <c r="N57" s="8" t="s">
-        <v>154</v>
+        <v>588</v>
       </c>
       <c r="O57" s="8" t="s">
-        <v>113</v>
+        <v>619</v>
       </c>
     </row>
     <row r="58" ht="NA" customHeight="1">
@@ -4112,46 +5068,46 @@
         <v>3</v>
       </c>
       <c r="B58" s="8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>114</v>
+        <v>138</v>
       </c>
       <c r="D58" s="8" t="s">
-        <v>147</v>
+        <v>193</v>
       </c>
       <c r="E58" s="8" t="s">
-        <v>169</v>
+        <v>238</v>
       </c>
       <c r="F58" s="8" t="s">
-        <v>189</v>
+        <v>277</v>
       </c>
       <c r="G58" s="8" t="s">
-        <v>211</v>
+        <v>324</v>
       </c>
       <c r="H58" s="8" t="s">
-        <v>227</v>
+        <v>365</v>
       </c>
       <c r="I58" s="8" t="s">
-        <v>243</v>
+        <v>410</v>
       </c>
       <c r="J58" s="8" t="s">
-        <v>255</v>
+        <v>445</v>
       </c>
       <c r="K58" s="8" t="s">
-        <v>269</v>
+        <v>485</v>
       </c>
       <c r="L58" s="8" t="s">
-        <v>278</v>
+        <v>519</v>
       </c>
       <c r="M58" s="8" t="s">
-        <v>289</v>
+        <v>553</v>
       </c>
       <c r="N58" s="8" t="s">
-        <v>298</v>
+        <v>585</v>
       </c>
       <c r="O58" s="8" t="s">
-        <v>311</v>
+        <v>616</v>
       </c>
     </row>
     <row r="59" ht="NA" customHeight="1">
@@ -4206,46 +5162,46 @@
         <v>1</v>
       </c>
       <c r="B60" s="8" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="C60" s="8" t="s">
-        <v>117</v>
+        <v>143</v>
       </c>
       <c r="D60" s="8" t="s">
-        <v>117</v>
+        <v>199</v>
       </c>
       <c r="E60" s="8" t="s">
-        <v>75</v>
+        <v>241</v>
       </c>
       <c r="F60" s="8" t="s">
-        <v>75</v>
+        <v>282</v>
       </c>
       <c r="G60" s="8" t="s">
-        <v>75</v>
+        <v>329</v>
       </c>
       <c r="H60" s="8" t="s">
-        <v>188</v>
+        <v>371</v>
       </c>
       <c r="I60" s="8" t="s">
-        <v>86</v>
+        <v>413</v>
       </c>
       <c r="J60" s="8" t="s">
-        <v>188</v>
+        <v>450</v>
       </c>
       <c r="K60" s="8" t="s">
-        <v>86</v>
+        <v>490</v>
       </c>
       <c r="L60" s="8" t="s">
-        <v>117</v>
+        <v>523</v>
       </c>
       <c r="M60" s="8" t="s">
-        <v>75</v>
+        <v>559</v>
       </c>
       <c r="N60" s="8" t="s">
-        <v>71</v>
+        <v>589</v>
       </c>
       <c r="O60" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="61" ht="NA" customHeight="1">
@@ -4253,46 +5209,46 @@
         <v>2</v>
       </c>
       <c r="B61" s="8" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="C61" s="8" t="s">
-        <v>118</v>
+        <v>144</v>
       </c>
       <c r="D61" s="8" t="s">
-        <v>87</v>
+        <v>200</v>
       </c>
       <c r="E61" s="8" t="s">
-        <v>170</v>
+        <v>242</v>
       </c>
       <c r="F61" s="8" t="s">
-        <v>170</v>
+        <v>283</v>
       </c>
       <c r="G61" s="8" t="s">
-        <v>170</v>
+        <v>330</v>
       </c>
       <c r="H61" s="8" t="s">
-        <v>118</v>
+        <v>372</v>
       </c>
       <c r="I61" s="8" t="s">
-        <v>87</v>
+        <v>414</v>
       </c>
       <c r="J61" s="8" t="s">
-        <v>170</v>
+        <v>451</v>
       </c>
       <c r="K61" s="8" t="s">
-        <v>87</v>
+        <v>491</v>
       </c>
       <c r="L61" s="8" t="s">
-        <v>118</v>
+        <v>524</v>
       </c>
       <c r="M61" s="8" t="s">
-        <v>91</v>
+        <v>560</v>
       </c>
       <c r="N61" s="8" t="s">
-        <v>215</v>
+        <v>590</v>
       </c>
       <c r="O61" s="8" t="s">
-        <v>91</v>
+        <v>560</v>
       </c>
     </row>
     <row r="62" ht="NA" customHeight="1">
@@ -4303,22 +5259,22 @@
         <v>67</v>
       </c>
       <c r="C62" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D62" s="8" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="E62" s="8" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="F62" s="8" t="s">
-        <v>191</v>
+        <v>284</v>
       </c>
       <c r="G62" s="8" t="s">
         <v>64</v>
       </c>
       <c r="H62" s="8" t="s">
-        <v>229</v>
+        <v>373</v>
       </c>
       <c r="I62" s="8" t="s">
         <v>66</v>
@@ -4339,7 +5295,7 @@
         <v>66</v>
       </c>
       <c r="O62" s="8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="63" ht="NA" customHeight="1">
@@ -4386,7 +5342,7 @@
         <v>0</v>
       </c>
       <c r="O63" s="8" t="s">
-        <v>312</v>
+        <v>620</v>
       </c>
     </row>
     <row r="64" ht="NA" customHeight="1">
@@ -4441,46 +5397,46 @@
         <v>1</v>
       </c>
       <c r="B65" s="8" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="C65" s="8" t="s">
-        <v>88</v>
+        <v>145</v>
       </c>
       <c r="D65" s="8" t="s">
-        <v>60</v>
+        <v>183</v>
       </c>
       <c r="E65" s="8" t="s">
-        <v>107</v>
+        <v>243</v>
       </c>
       <c r="F65" s="8" t="s">
-        <v>192</v>
+        <v>285</v>
       </c>
       <c r="G65" s="8" t="s">
-        <v>212</v>
+        <v>331</v>
       </c>
       <c r="H65" s="8" t="s">
-        <v>230</v>
+        <v>374</v>
       </c>
       <c r="I65" s="8" t="s">
-        <v>186</v>
+        <v>266</v>
       </c>
       <c r="J65" s="8" t="s">
-        <v>256</v>
+        <v>452</v>
       </c>
       <c r="K65" s="8" t="s">
-        <v>258</v>
+        <v>455</v>
       </c>
       <c r="L65" s="8" t="s">
-        <v>256</v>
+        <v>452</v>
       </c>
       <c r="M65" s="8" t="s">
-        <v>172</v>
+        <v>245</v>
       </c>
       <c r="N65" s="8" t="s">
-        <v>299</v>
+        <v>591</v>
       </c>
       <c r="O65" s="8" t="s">
-        <v>299</v>
+        <v>591</v>
       </c>
     </row>
     <row r="66" ht="NA" customHeight="1">
@@ -4488,46 +5444,46 @@
         <v>2</v>
       </c>
       <c r="B66" s="8" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="C66" s="8" t="s">
-        <v>119</v>
+        <v>146</v>
       </c>
       <c r="D66" s="8" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="E66" s="8" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="F66" s="8" t="s">
-        <v>137</v>
+        <v>174</v>
       </c>
       <c r="G66" s="8" t="s">
-        <v>213</v>
+        <v>332</v>
       </c>
       <c r="H66" s="8" t="s">
-        <v>213</v>
+        <v>332</v>
       </c>
       <c r="I66" s="8" t="s">
-        <v>222</v>
+        <v>353</v>
       </c>
       <c r="J66" s="8" t="s">
-        <v>257</v>
+        <v>453</v>
       </c>
       <c r="K66" s="8" t="s">
-        <v>213</v>
+        <v>332</v>
       </c>
       <c r="L66" s="8" t="s">
-        <v>164</v>
+        <v>223</v>
       </c>
       <c r="M66" s="8" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="N66" s="8" t="s">
-        <v>137</v>
+        <v>174</v>
       </c>
       <c r="O66" s="8" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
     </row>
     <row r="67" ht="NA" customHeight="1">
@@ -4535,46 +5491,46 @@
         <v>3</v>
       </c>
       <c r="B67" s="8" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C67" s="8" t="s">
-        <v>90</v>
+        <v>147</v>
       </c>
       <c r="D67" s="8" t="s">
-        <v>148</v>
+        <v>201</v>
       </c>
       <c r="E67" s="8" t="s">
-        <v>171</v>
+        <v>244</v>
       </c>
       <c r="F67" s="8" t="s">
-        <v>193</v>
+        <v>286</v>
       </c>
       <c r="G67" s="8" t="s">
-        <v>193</v>
+        <v>333</v>
       </c>
       <c r="H67" s="8" t="s">
-        <v>231</v>
+        <v>375</v>
       </c>
       <c r="I67" s="8" t="s">
-        <v>231</v>
+        <v>415</v>
       </c>
       <c r="J67" s="8" t="s">
-        <v>231</v>
+        <v>454</v>
       </c>
       <c r="K67" s="8" t="s">
-        <v>245</v>
+        <v>492</v>
       </c>
       <c r="L67" s="8" t="s">
-        <v>231</v>
+        <v>525</v>
       </c>
       <c r="M67" s="8" t="s">
-        <v>245</v>
+        <v>561</v>
       </c>
       <c r="N67" s="8" t="s">
-        <v>245</v>
+        <v>592</v>
       </c>
       <c r="O67" s="8" t="s">
-        <v>245</v>
+        <v>492</v>
       </c>
     </row>
     <row r="68" ht="NA" customHeight="1">
@@ -4679,43 +5635,43 @@
         <v>57</v>
       </c>
       <c r="C70" s="8" t="s">
-        <v>72</v>
+        <v>148</v>
       </c>
       <c r="D70" s="8" t="s">
-        <v>72</v>
+        <v>148</v>
       </c>
       <c r="E70" s="8" t="s">
-        <v>72</v>
+        <v>148</v>
       </c>
       <c r="F70" s="8" t="s">
-        <v>72</v>
+        <v>197</v>
       </c>
       <c r="G70" s="8" t="s">
-        <v>57</v>
+        <v>334</v>
       </c>
       <c r="H70" s="8" t="s">
-        <v>57</v>
+        <v>376</v>
       </c>
       <c r="I70" s="8" t="s">
-        <v>75</v>
+        <v>416</v>
       </c>
       <c r="J70" s="8" t="s">
-        <v>72</v>
+        <v>148</v>
       </c>
       <c r="K70" s="8" t="s">
-        <v>57</v>
+        <v>226</v>
       </c>
       <c r="L70" s="8" t="s">
-        <v>57</v>
+        <v>179</v>
       </c>
       <c r="M70" s="8" t="s">
-        <v>57</v>
+        <v>218</v>
       </c>
       <c r="N70" s="8" t="s">
-        <v>75</v>
+        <v>593</v>
       </c>
       <c r="O70" s="8" t="s">
-        <v>117</v>
+        <v>621</v>
       </c>
     </row>
     <row r="71" ht="NA" customHeight="1">
@@ -4723,46 +5679,46 @@
         <v>2</v>
       </c>
       <c r="B71" s="8" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="C71" s="8" t="s">
-        <v>120</v>
+        <v>149</v>
       </c>
       <c r="D71" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="E71" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="F71" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="E71" s="8" t="s">
+      <c r="G71" s="8" t="s">
+        <v>335</v>
+      </c>
+      <c r="H71" s="8" t="s">
+        <v>377</v>
+      </c>
+      <c r="I71" s="8" t="s">
+        <v>417</v>
+      </c>
+      <c r="J71" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="F71" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="G71" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="H71" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="I71" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="J71" s="8" t="s">
-        <v>120</v>
-      </c>
       <c r="K71" s="8" t="s">
-        <v>149</v>
+        <v>493</v>
       </c>
       <c r="L71" s="8" t="s">
-        <v>149</v>
+        <v>526</v>
       </c>
       <c r="M71" s="8" t="s">
-        <v>149</v>
+        <v>562</v>
       </c>
       <c r="N71" s="8" t="s">
-        <v>91</v>
+        <v>594</v>
       </c>
       <c r="O71" s="8" t="s">
-        <v>118</v>
+        <v>622</v>
       </c>
     </row>
     <row r="72" ht="NA" customHeight="1">
@@ -4770,34 +5726,34 @@
         <v>777</v>
       </c>
       <c r="B72" s="8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C72" s="8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D72" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E72" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F72" s="8" t="s">
-        <v>168</v>
+        <v>237</v>
       </c>
       <c r="G72" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H72" s="8" t="s">
         <v>67</v>
       </c>
       <c r="I72" s="8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J72" s="8" t="s">
         <v>67</v>
       </c>
       <c r="K72" s="8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="L72" s="8" t="s">
         <v>67</v>
@@ -4806,10 +5762,10 @@
         <v>66</v>
       </c>
       <c r="N72" s="8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O72" s="8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="73" ht="NA" customHeight="1">
@@ -4911,46 +5867,46 @@
         <v>1</v>
       </c>
       <c r="B75" s="8" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="C75" s="8" t="s">
-        <v>121</v>
+        <v>150</v>
       </c>
       <c r="D75" s="8" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E75" s="8" t="s">
-        <v>172</v>
+        <v>245</v>
       </c>
       <c r="F75" s="8" t="s">
-        <v>194</v>
+        <v>287</v>
       </c>
       <c r="G75" s="8" t="s">
-        <v>123</v>
+        <v>152</v>
       </c>
       <c r="H75" s="8" t="s">
-        <v>172</v>
+        <v>245</v>
       </c>
       <c r="I75" s="8" t="s">
-        <v>244</v>
+        <v>418</v>
       </c>
       <c r="J75" s="8" t="s">
-        <v>258</v>
+        <v>455</v>
       </c>
       <c r="K75" s="8" t="s">
-        <v>270</v>
+        <v>494</v>
       </c>
       <c r="L75" s="8" t="s">
-        <v>172</v>
+        <v>245</v>
       </c>
       <c r="M75" s="8" t="s">
-        <v>112</v>
+        <v>132</v>
       </c>
       <c r="N75" s="8" t="s">
-        <v>212</v>
+        <v>331</v>
       </c>
       <c r="O75" s="8" t="s">
-        <v>107</v>
+        <v>171</v>
       </c>
     </row>
     <row r="76" ht="NA" customHeight="1">
@@ -4958,46 +5914,46 @@
         <v>2</v>
       </c>
       <c r="B76" s="8" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="C76" s="8" t="s">
-        <v>122</v>
+        <v>151</v>
       </c>
       <c r="D76" s="8" t="s">
-        <v>93</v>
+        <v>203</v>
       </c>
       <c r="E76" s="8" t="s">
-        <v>173</v>
+        <v>246</v>
       </c>
       <c r="F76" s="8" t="s">
-        <v>173</v>
+        <v>288</v>
       </c>
       <c r="G76" s="8" t="s">
-        <v>123</v>
+        <v>152</v>
       </c>
       <c r="H76" s="8" t="s">
-        <v>173</v>
+        <v>378</v>
       </c>
       <c r="I76" s="8" t="s">
-        <v>245</v>
+        <v>419</v>
       </c>
       <c r="J76" s="8" t="s">
-        <v>173</v>
+        <v>378</v>
       </c>
       <c r="K76" s="8" t="s">
-        <v>173</v>
+        <v>378</v>
       </c>
       <c r="L76" s="8" t="s">
-        <v>173</v>
+        <v>527</v>
       </c>
       <c r="M76" s="8" t="s">
-        <v>173</v>
+        <v>563</v>
       </c>
       <c r="N76" s="8" t="s">
-        <v>245</v>
+        <v>492</v>
       </c>
       <c r="O76" s="8" t="s">
-        <v>231</v>
+        <v>623</v>
       </c>
     </row>
     <row r="77" ht="NA" customHeight="1">
@@ -5005,25 +5961,25 @@
         <v>777</v>
       </c>
       <c r="B77" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C77" s="8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D77" s="8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E77" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F77" s="8" t="s">
-        <v>138</v>
+        <v>175</v>
       </c>
       <c r="G77" s="8" t="s">
-        <v>123</v>
+        <v>152</v>
       </c>
       <c r="H77" s="8" t="s">
-        <v>168</v>
+        <v>237</v>
       </c>
       <c r="I77" s="8" t="s">
         <v>66</v>
@@ -5032,7 +5988,7 @@
         <v>67</v>
       </c>
       <c r="K77" s="8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="L77" s="8" t="s">
         <v>67</v>
@@ -5067,7 +6023,7 @@
         <v>0</v>
       </c>
       <c r="G78" s="8" t="s">
-        <v>214</v>
+        <v>336</v>
       </c>
       <c r="H78" s="8" t="n">
         <v>0</v>
@@ -5146,46 +6102,46 @@
         <v>1</v>
       </c>
       <c r="B80" s="8" t="s">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="C80" s="8" t="s">
-        <v>123</v>
+        <v>152</v>
       </c>
       <c r="D80" s="8" t="s">
-        <v>123</v>
+        <v>152</v>
       </c>
       <c r="E80" s="8" t="s">
-        <v>123</v>
+        <v>152</v>
       </c>
       <c r="F80" s="8" t="s">
-        <v>58</v>
+        <v>289</v>
       </c>
       <c r="G80" s="8" t="s">
-        <v>58</v>
+        <v>168</v>
       </c>
       <c r="H80" s="8" t="s">
-        <v>165</v>
+        <v>379</v>
       </c>
       <c r="I80" s="8" t="s">
-        <v>116</v>
+        <v>420</v>
       </c>
       <c r="J80" s="8" t="s">
-        <v>123</v>
+        <v>152</v>
       </c>
       <c r="K80" s="8" t="s">
-        <v>123</v>
+        <v>152</v>
       </c>
       <c r="L80" s="8" t="s">
-        <v>123</v>
+        <v>152</v>
       </c>
       <c r="M80" s="8" t="s">
-        <v>123</v>
+        <v>152</v>
       </c>
       <c r="N80" s="8" t="s">
-        <v>123</v>
+        <v>152</v>
       </c>
       <c r="O80" s="8" t="s">
-        <v>123</v>
+        <v>152</v>
       </c>
     </row>
     <row r="81" ht="NA" customHeight="1">
@@ -5193,46 +6149,46 @@
         <v>2</v>
       </c>
       <c r="B81" s="8" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="C81" s="8" t="s">
-        <v>123</v>
+        <v>152</v>
       </c>
       <c r="D81" s="8" t="s">
-        <v>123</v>
+        <v>152</v>
       </c>
       <c r="E81" s="8" t="s">
-        <v>123</v>
+        <v>152</v>
       </c>
       <c r="F81" s="8" t="s">
-        <v>195</v>
+        <v>290</v>
       </c>
       <c r="G81" s="8" t="s">
-        <v>215</v>
+        <v>337</v>
       </c>
       <c r="H81" s="8" t="s">
-        <v>232</v>
+        <v>380</v>
       </c>
       <c r="I81" s="8" t="s">
-        <v>232</v>
+        <v>421</v>
       </c>
       <c r="J81" s="8" t="s">
-        <v>123</v>
+        <v>152</v>
       </c>
       <c r="K81" s="8" t="s">
-        <v>123</v>
+        <v>152</v>
       </c>
       <c r="L81" s="8" t="s">
-        <v>123</v>
+        <v>152</v>
       </c>
       <c r="M81" s="8" t="s">
-        <v>123</v>
+        <v>152</v>
       </c>
       <c r="N81" s="8" t="s">
-        <v>123</v>
+        <v>152</v>
       </c>
       <c r="O81" s="8" t="s">
-        <v>123</v>
+        <v>152</v>
       </c>
     </row>
     <row r="82" ht="NA" customHeight="1">
@@ -5240,46 +6196,46 @@
         <v>777</v>
       </c>
       <c r="B82" s="8" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="C82" s="8" t="s">
-        <v>123</v>
+        <v>152</v>
       </c>
       <c r="D82" s="8" t="s">
-        <v>123</v>
+        <v>152</v>
       </c>
       <c r="E82" s="8" t="s">
-        <v>123</v>
+        <v>152</v>
       </c>
       <c r="F82" s="8" t="s">
-        <v>196</v>
+        <v>291</v>
       </c>
       <c r="G82" s="8" t="s">
-        <v>185</v>
+        <v>265</v>
       </c>
       <c r="H82" s="8" t="s">
-        <v>222</v>
+        <v>353</v>
       </c>
       <c r="I82" s="8" t="s">
-        <v>229</v>
+        <v>373</v>
       </c>
       <c r="J82" s="8" t="s">
-        <v>123</v>
+        <v>152</v>
       </c>
       <c r="K82" s="8" t="s">
-        <v>123</v>
+        <v>152</v>
       </c>
       <c r="L82" s="8" t="s">
-        <v>123</v>
+        <v>152</v>
       </c>
       <c r="M82" s="8" t="s">
-        <v>123</v>
+        <v>152</v>
       </c>
       <c r="N82" s="8" t="s">
-        <v>123</v>
+        <v>152</v>
       </c>
       <c r="O82" s="8" t="s">
-        <v>123</v>
+        <v>152</v>
       </c>
     </row>
     <row r="83" ht="NA" customHeight="1">
@@ -5290,13 +6246,13 @@
         <v>0</v>
       </c>
       <c r="C83" s="8" t="s">
-        <v>124</v>
+        <v>153</v>
       </c>
       <c r="D83" s="8" t="s">
-        <v>150</v>
+        <v>204</v>
       </c>
       <c r="E83" s="8" t="s">
-        <v>174</v>
+        <v>247</v>
       </c>
       <c r="F83" s="8" t="n">
         <v>0</v>
@@ -5311,22 +6267,22 @@
         <v>0</v>
       </c>
       <c r="J83" s="8" t="s">
-        <v>259</v>
+        <v>456</v>
       </c>
       <c r="K83" s="8" t="s">
-        <v>271</v>
+        <v>495</v>
       </c>
       <c r="L83" s="8" t="s">
-        <v>279</v>
+        <v>528</v>
       </c>
       <c r="M83" s="8" t="s">
-        <v>290</v>
+        <v>564</v>
       </c>
       <c r="N83" s="8" t="s">
-        <v>300</v>
+        <v>595</v>
       </c>
       <c r="O83" s="8" t="s">
-        <v>313</v>
+        <v>624</v>
       </c>
     </row>
     <row r="84" ht="NA" customHeight="1">
@@ -5334,46 +6290,46 @@
         <v>36</v>
       </c>
       <c r="B84" s="8" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="C84" s="8" t="s">
-        <v>125</v>
+        <v>154</v>
       </c>
       <c r="D84" s="8" t="s">
-        <v>151</v>
+        <v>205</v>
       </c>
       <c r="E84" s="8" t="s">
-        <v>175</v>
+        <v>248</v>
       </c>
       <c r="F84" s="8" t="s">
-        <v>197</v>
+        <v>292</v>
       </c>
       <c r="G84" s="8" t="s">
-        <v>216</v>
+        <v>338</v>
       </c>
       <c r="H84" s="8" t="s">
-        <v>233</v>
+        <v>381</v>
       </c>
       <c r="I84" s="8" t="s">
-        <v>246</v>
+        <v>422</v>
       </c>
       <c r="J84" s="8" t="s">
-        <v>260</v>
+        <v>457</v>
       </c>
       <c r="K84" s="8" t="s">
-        <v>272</v>
+        <v>496</v>
       </c>
       <c r="L84" s="8" t="s">
-        <v>280</v>
+        <v>529</v>
       </c>
       <c r="M84" s="8" t="s">
-        <v>291</v>
+        <v>565</v>
       </c>
       <c r="N84" s="8" t="s">
-        <v>301</v>
+        <v>596</v>
       </c>
       <c r="O84" s="8" t="s">
-        <v>314</v>
+        <v>625</v>
       </c>
     </row>
     <row r="85" ht="NA" customHeight="1">
@@ -5381,46 +6337,46 @@
         <v>37</v>
       </c>
       <c r="B85" s="8" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="C85" s="8" t="s">
-        <v>97</v>
+        <v>155</v>
       </c>
       <c r="D85" s="8" t="s">
-        <v>152</v>
+        <v>206</v>
       </c>
       <c r="E85" s="8" t="s">
-        <v>176</v>
+        <v>249</v>
       </c>
       <c r="F85" s="8" t="s">
-        <v>198</v>
+        <v>293</v>
       </c>
       <c r="G85" s="8" t="s">
-        <v>198</v>
+        <v>339</v>
       </c>
       <c r="H85" s="8" t="s">
-        <v>234</v>
+        <v>382</v>
       </c>
       <c r="I85" s="8" t="s">
-        <v>247</v>
+        <v>423</v>
       </c>
       <c r="J85" s="8" t="s">
-        <v>247</v>
+        <v>458</v>
       </c>
       <c r="K85" s="8" t="s">
-        <v>247</v>
+        <v>497</v>
       </c>
       <c r="L85" s="8" t="s">
-        <v>281</v>
+        <v>530</v>
       </c>
       <c r="M85" s="8" t="s">
-        <v>247</v>
+        <v>566</v>
       </c>
       <c r="N85" s="8" t="s">
-        <v>302</v>
+        <v>597</v>
       </c>
       <c r="O85" s="8" t="s">
-        <v>234</v>
+        <v>626</v>
       </c>
     </row>
     <row r="86" ht="NA" customHeight="1">
@@ -5475,46 +6431,46 @@
         <v>39</v>
       </c>
       <c r="B87" s="8" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="C87" s="8" t="s">
-        <v>94</v>
+        <v>156</v>
       </c>
       <c r="D87" s="8" t="s">
-        <v>153</v>
+        <v>207</v>
       </c>
       <c r="E87" s="8" t="s">
-        <v>177</v>
+        <v>250</v>
       </c>
       <c r="F87" s="8" t="s">
-        <v>148</v>
+        <v>294</v>
       </c>
       <c r="G87" s="8" t="s">
-        <v>148</v>
+        <v>294</v>
       </c>
       <c r="H87" s="8" t="s">
-        <v>148</v>
+        <v>383</v>
       </c>
       <c r="I87" s="8" t="s">
-        <v>177</v>
+        <v>424</v>
       </c>
       <c r="J87" s="8" t="s">
-        <v>90</v>
+        <v>459</v>
       </c>
       <c r="K87" s="8" t="s">
-        <v>177</v>
+        <v>498</v>
       </c>
       <c r="L87" s="8" t="s">
-        <v>177</v>
+        <v>531</v>
       </c>
       <c r="M87" s="8" t="s">
-        <v>90</v>
+        <v>147</v>
       </c>
       <c r="N87" s="8" t="s">
-        <v>193</v>
+        <v>333</v>
       </c>
       <c r="O87" s="8" t="s">
-        <v>148</v>
+        <v>627</v>
       </c>
     </row>
     <row r="88" ht="NA" customHeight="1">
@@ -5522,46 +6478,46 @@
         <v>40</v>
       </c>
       <c r="B88" s="8" t="s">
-        <v>70</v>
+        <v>106</v>
       </c>
       <c r="C88" s="8" t="s">
-        <v>126</v>
+        <v>157</v>
       </c>
       <c r="D88" s="8" t="s">
-        <v>59</v>
+        <v>208</v>
       </c>
       <c r="E88" s="8" t="s">
-        <v>76</v>
+        <v>185</v>
       </c>
       <c r="F88" s="8" t="s">
-        <v>199</v>
+        <v>295</v>
       </c>
       <c r="G88" s="8" t="s">
-        <v>199</v>
+        <v>295</v>
       </c>
       <c r="H88" s="8" t="s">
-        <v>199</v>
+        <v>384</v>
       </c>
       <c r="I88" s="8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J88" s="8" t="s">
-        <v>226</v>
+        <v>460</v>
       </c>
       <c r="K88" s="8" t="s">
-        <v>76</v>
+        <v>499</v>
       </c>
       <c r="L88" s="8" t="s">
-        <v>76</v>
+        <v>393</v>
       </c>
       <c r="M88" s="8" t="s">
-        <v>226</v>
+        <v>470</v>
       </c>
       <c r="N88" s="8" t="s">
-        <v>60</v>
+        <v>348</v>
       </c>
       <c r="O88" s="8" t="s">
-        <v>199</v>
+        <v>628</v>
       </c>
     </row>
     <row r="89" ht="NA" customHeight="1">
@@ -5569,46 +6525,46 @@
         <v>41</v>
       </c>
       <c r="B89" s="8" t="s">
-        <v>70</v>
+        <v>106</v>
       </c>
       <c r="C89" s="8" t="s">
-        <v>126</v>
+        <v>157</v>
       </c>
       <c r="D89" s="8" t="s">
-        <v>59</v>
+        <v>208</v>
       </c>
       <c r="E89" s="8" t="s">
-        <v>76</v>
+        <v>185</v>
       </c>
       <c r="F89" s="8" t="s">
-        <v>199</v>
+        <v>295</v>
       </c>
       <c r="G89" s="8" t="s">
-        <v>199</v>
+        <v>295</v>
       </c>
       <c r="H89" s="8" t="s">
-        <v>199</v>
+        <v>384</v>
       </c>
       <c r="I89" s="8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J89" s="8" t="s">
-        <v>226</v>
+        <v>460</v>
       </c>
       <c r="K89" s="8" t="s">
-        <v>76</v>
+        <v>499</v>
       </c>
       <c r="L89" s="8" t="s">
-        <v>76</v>
+        <v>393</v>
       </c>
       <c r="M89" s="8" t="s">
-        <v>226</v>
+        <v>470</v>
       </c>
       <c r="N89" s="8" t="s">
-        <v>60</v>
+        <v>348</v>
       </c>
       <c r="O89" s="8" t="s">
-        <v>199</v>
+        <v>628</v>
       </c>
     </row>
     <row r="90" ht="NA" customHeight="1">
@@ -5663,46 +6619,46 @@
         <v>43</v>
       </c>
       <c r="B91" s="8" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="C91" s="8" t="s">
-        <v>127</v>
+        <v>158</v>
       </c>
       <c r="D91" s="8" t="s">
-        <v>154</v>
+        <v>209</v>
       </c>
       <c r="E91" s="8" t="s">
-        <v>79</v>
+        <v>251</v>
       </c>
       <c r="F91" s="8" t="s">
-        <v>142</v>
+        <v>296</v>
       </c>
       <c r="G91" s="8" t="s">
-        <v>142</v>
+        <v>340</v>
       </c>
       <c r="H91" s="8" t="s">
-        <v>235</v>
+        <v>385</v>
       </c>
       <c r="I91" s="8" t="s">
-        <v>142</v>
+        <v>187</v>
       </c>
       <c r="J91" s="8" t="s">
-        <v>235</v>
+        <v>461</v>
       </c>
       <c r="K91" s="8" t="s">
-        <v>235</v>
+        <v>500</v>
       </c>
       <c r="L91" s="8" t="s">
-        <v>235</v>
+        <v>532</v>
       </c>
       <c r="M91" s="8" t="s">
-        <v>292</v>
+        <v>567</v>
       </c>
       <c r="N91" s="8" t="s">
-        <v>118</v>
+        <v>598</v>
       </c>
       <c r="O91" s="8" t="s">
-        <v>87</v>
+        <v>491</v>
       </c>
     </row>
     <row r="92" ht="NA" customHeight="1">
@@ -5710,46 +6666,46 @@
         <v>44</v>
       </c>
       <c r="B92" s="8" t="s">
-        <v>100</v>
+        <v>66</v>
       </c>
       <c r="C92" s="8" t="s">
-        <v>100</v>
+        <v>66</v>
       </c>
       <c r="D92" s="8" t="s">
-        <v>100</v>
+        <v>66</v>
       </c>
       <c r="E92" s="8" t="s">
-        <v>100</v>
+        <v>66</v>
       </c>
       <c r="F92" s="8" t="s">
-        <v>100</v>
+        <v>66</v>
       </c>
       <c r="G92" s="8" t="s">
-        <v>100</v>
+        <v>66</v>
       </c>
       <c r="H92" s="8" t="s">
-        <v>100</v>
+        <v>66</v>
       </c>
       <c r="I92" s="8" t="s">
-        <v>100</v>
+        <v>66</v>
       </c>
       <c r="J92" s="8" t="s">
-        <v>100</v>
+        <v>66</v>
       </c>
       <c r="K92" s="8" t="s">
-        <v>100</v>
+        <v>66</v>
       </c>
       <c r="L92" s="8" t="s">
-        <v>100</v>
+        <v>66</v>
       </c>
       <c r="M92" s="8" t="s">
-        <v>100</v>
+        <v>66</v>
       </c>
       <c r="N92" s="8" t="s">
-        <v>100</v>
+        <v>66</v>
       </c>
       <c r="O92" s="8" t="s">
-        <v>100</v>
+        <v>66</v>
       </c>
     </row>
     <row r="93" ht="NA" customHeight="1">
@@ -5757,46 +6713,46 @@
         <v>45</v>
       </c>
       <c r="B93" s="8" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="C93" s="8" t="s">
-        <v>128</v>
+        <v>159</v>
       </c>
       <c r="D93" s="8" t="s">
-        <v>155</v>
+        <v>210</v>
       </c>
       <c r="E93" s="8" t="s">
-        <v>178</v>
+        <v>252</v>
       </c>
       <c r="F93" s="8" t="s">
-        <v>200</v>
+        <v>297</v>
       </c>
       <c r="G93" s="8" t="s">
-        <v>200</v>
+        <v>297</v>
       </c>
       <c r="H93" s="8" t="s">
-        <v>200</v>
+        <v>297</v>
       </c>
       <c r="I93" s="8" t="s">
-        <v>248</v>
+        <v>425</v>
       </c>
       <c r="J93" s="8" t="s">
-        <v>261</v>
+        <v>462</v>
       </c>
       <c r="K93" s="8" t="s">
-        <v>221</v>
+        <v>351</v>
       </c>
       <c r="L93" s="8" t="s">
-        <v>261</v>
+        <v>462</v>
       </c>
       <c r="M93" s="8" t="s">
-        <v>221</v>
+        <v>351</v>
       </c>
       <c r="N93" s="8" t="s">
-        <v>303</v>
+        <v>599</v>
       </c>
       <c r="O93" s="8" t="s">
-        <v>315</v>
+        <v>629</v>
       </c>
     </row>
     <row r="94" ht="NA" customHeight="1">
@@ -5804,46 +6760,46 @@
         <v>46</v>
       </c>
       <c r="B94" s="8" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="C94" s="8" t="s">
-        <v>129</v>
+        <v>160</v>
       </c>
       <c r="D94" s="8" t="s">
-        <v>156</v>
+        <v>211</v>
       </c>
       <c r="E94" s="8" t="s">
-        <v>179</v>
+        <v>253</v>
       </c>
       <c r="F94" s="8" t="s">
-        <v>82</v>
+        <v>298</v>
       </c>
       <c r="G94" s="8" t="s">
-        <v>145</v>
+        <v>341</v>
       </c>
       <c r="H94" s="8" t="s">
-        <v>86</v>
+        <v>386</v>
       </c>
       <c r="I94" s="8" t="s">
-        <v>145</v>
+        <v>191</v>
       </c>
       <c r="J94" s="8" t="s">
-        <v>86</v>
+        <v>463</v>
       </c>
       <c r="K94" s="8" t="s">
-        <v>82</v>
+        <v>501</v>
       </c>
       <c r="L94" s="8" t="s">
-        <v>82</v>
+        <v>533</v>
       </c>
       <c r="M94" s="8" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="N94" s="8" t="s">
-        <v>72</v>
+        <v>197</v>
       </c>
       <c r="O94" s="8" t="s">
-        <v>75</v>
+        <v>416</v>
       </c>
     </row>
     <row r="95" ht="NA" customHeight="1">
@@ -5898,46 +6854,46 @@
         <v>39</v>
       </c>
       <c r="B96" s="8" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="C96" s="8" t="s">
-        <v>94</v>
+        <v>156</v>
       </c>
       <c r="D96" s="8" t="s">
-        <v>153</v>
+        <v>207</v>
       </c>
       <c r="E96" s="8" t="s">
-        <v>177</v>
+        <v>250</v>
       </c>
       <c r="F96" s="8" t="s">
-        <v>148</v>
+        <v>294</v>
       </c>
       <c r="G96" s="8" t="s">
-        <v>148</v>
+        <v>294</v>
       </c>
       <c r="H96" s="8" t="s">
-        <v>148</v>
+        <v>383</v>
       </c>
       <c r="I96" s="8" t="s">
-        <v>177</v>
+        <v>424</v>
       </c>
       <c r="J96" s="8" t="s">
-        <v>90</v>
+        <v>459</v>
       </c>
       <c r="K96" s="8" t="s">
-        <v>177</v>
+        <v>498</v>
       </c>
       <c r="L96" s="8" t="s">
-        <v>177</v>
+        <v>531</v>
       </c>
       <c r="M96" s="8" t="s">
-        <v>90</v>
+        <v>147</v>
       </c>
       <c r="N96" s="8" t="s">
-        <v>193</v>
+        <v>333</v>
       </c>
       <c r="O96" s="8" t="s">
-        <v>148</v>
+        <v>627</v>
       </c>
     </row>
     <row r="97" ht="NA" customHeight="1">
@@ -5945,46 +6901,46 @@
         <v>40</v>
       </c>
       <c r="B97" s="9" t="s">
-        <v>70</v>
+        <v>106</v>
       </c>
       <c r="C97" s="9" t="s">
-        <v>126</v>
+        <v>157</v>
       </c>
       <c r="D97" s="9" t="s">
-        <v>59</v>
+        <v>208</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>76</v>
+        <v>185</v>
       </c>
       <c r="F97" s="9" t="s">
-        <v>199</v>
+        <v>295</v>
       </c>
       <c r="G97" s="9" t="s">
-        <v>199</v>
+        <v>295</v>
       </c>
       <c r="H97" s="9" t="s">
-        <v>199</v>
+        <v>384</v>
       </c>
       <c r="I97" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J97" s="9" t="s">
-        <v>226</v>
+        <v>460</v>
       </c>
       <c r="K97" s="9" t="s">
-        <v>76</v>
+        <v>499</v>
       </c>
       <c r="L97" s="9" t="s">
-        <v>76</v>
+        <v>393</v>
       </c>
       <c r="M97" s="9" t="s">
-        <v>226</v>
+        <v>470</v>
       </c>
       <c r="N97" s="9" t="s">
-        <v>60</v>
+        <v>348</v>
       </c>
       <c r="O97" s="9" t="s">
-        <v>199</v>
+        <v>628</v>
       </c>
     </row>
     <row r="98" ht="NA" customHeight="1">
